--- a/Data/Hires/Workday_NewHire_Spain_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Spain_Regression_PK17.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57CAB1BC-F320-49A1-A0DD-6C8BF9816CA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6162A306-448A-42BC-8CC8-123B2B3076D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="7360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="118">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -222,18 +222,9 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t>10698999</t>
-  </si>
-  <si>
-    <t>Passed</t>
-  </si>
-  <si>
     <t>356 Recruitment (Posob Zujefy Pyronu (2577) (Inherited))</t>
   </si>
   <si>
-    <t>SLName</t>
-  </si>
-  <si>
     <t>Spain</t>
   </si>
   <si>
@@ -346,9 +337,6 @@
   </si>
   <si>
     <t>Test_2</t>
-  </si>
-  <si>
-    <t>10699000</t>
   </si>
   <si>
     <t>365 Store Management (Cisuw Hapagu Pahame (10274587))</t>
@@ -395,6 +383,9 @@
   </si>
   <si>
     <t>Schinner</t>
+  </si>
+  <si>
+    <t>SLNameOne</t>
   </si>
 </sst>
 </file>
@@ -1013,87 +1004,87 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BZ54"/>
-  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" customWidth="1"/>
-    <col min="2" max="2" width="11.109375" customWidth="1"/>
-    <col min="3" max="3" width="10.21875" customWidth="1"/>
-    <col min="4" max="4" width="41.44140625" customWidth="1"/>
+    <col min="1" max="1" width="11.36328125" customWidth="1"/>
+    <col min="2" max="2" width="11.08984375" customWidth="1"/>
+    <col min="3" max="3" width="10.1796875" customWidth="1"/>
+    <col min="4" max="4" width="41.453125" customWidth="1"/>
     <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="13.44140625" customWidth="1"/>
-    <col min="7" max="7" width="21.77734375" customWidth="1"/>
-    <col min="8" max="8" width="13.44140625" customWidth="1"/>
+    <col min="6" max="6" width="13.453125" customWidth="1"/>
+    <col min="7" max="7" width="21.81640625" customWidth="1"/>
+    <col min="8" max="8" width="13.453125" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="5.6640625" customWidth="1"/>
-    <col min="11" max="11" width="12.44140625" customWidth="1"/>
-    <col min="12" max="12" width="12.21875" customWidth="1"/>
-    <col min="13" max="13" width="20.6640625" customWidth="1"/>
-    <col min="14" max="14" width="12.6640625" customWidth="1"/>
-    <col min="15" max="15" width="10.77734375" customWidth="1"/>
-    <col min="16" max="16" width="8.109375" customWidth="1"/>
-    <col min="17" max="17" width="13.21875" customWidth="1"/>
-    <col min="18" max="18" width="11.88671875" customWidth="1"/>
-    <col min="19" max="19" width="8.109375" customWidth="1"/>
-    <col min="20" max="20" width="5.6640625" customWidth="1"/>
-    <col min="21" max="21" width="12.33203125" customWidth="1"/>
+    <col min="10" max="10" width="5.6328125" customWidth="1"/>
+    <col min="11" max="11" width="12.453125" customWidth="1"/>
+    <col min="12" max="12" width="12.1796875" customWidth="1"/>
+    <col min="13" max="13" width="20.6328125" customWidth="1"/>
+    <col min="14" max="14" width="12.6328125" customWidth="1"/>
+    <col min="15" max="15" width="10.81640625" customWidth="1"/>
+    <col min="16" max="16" width="8.08984375" customWidth="1"/>
+    <col min="17" max="17" width="13.1796875" customWidth="1"/>
+    <col min="18" max="18" width="11.90625" customWidth="1"/>
+    <col min="19" max="19" width="8.08984375" customWidth="1"/>
+    <col min="20" max="20" width="5.6328125" customWidth="1"/>
+    <col min="21" max="21" width="12.36328125" customWidth="1"/>
     <col min="22" max="22" width="17" customWidth="1"/>
-    <col min="23" max="24" width="10.5546875" customWidth="1"/>
-    <col min="25" max="25" width="8.109375" customWidth="1"/>
-    <col min="26" max="26" width="23.109375" customWidth="1"/>
-    <col min="27" max="27" width="19.6640625" style="1" customWidth="1"/>
-    <col min="28" max="28" width="9.21875" customWidth="1"/>
-    <col min="29" max="29" width="9.21875" style="1" customWidth="1"/>
-    <col min="30" max="30" width="8.44140625" customWidth="1"/>
-    <col min="31" max="31" width="12.109375" customWidth="1"/>
-    <col min="32" max="32" width="9.44140625" customWidth="1"/>
-    <col min="33" max="33" width="11.21875" customWidth="1"/>
-    <col min="34" max="34" width="22.88671875" customWidth="1"/>
-    <col min="35" max="35" width="15.21875" customWidth="1"/>
-    <col min="36" max="36" width="14.109375" customWidth="1"/>
+    <col min="23" max="24" width="10.54296875" customWidth="1"/>
+    <col min="25" max="25" width="8.08984375" customWidth="1"/>
+    <col min="26" max="26" width="23.08984375" customWidth="1"/>
+    <col min="27" max="27" width="19.6328125" style="1" customWidth="1"/>
+    <col min="28" max="28" width="9.1796875" customWidth="1"/>
+    <col min="29" max="29" width="9.1796875" style="1" customWidth="1"/>
+    <col min="30" max="30" width="8.453125" customWidth="1"/>
+    <col min="31" max="31" width="12.08984375" customWidth="1"/>
+    <col min="32" max="32" width="9.453125" customWidth="1"/>
+    <col min="33" max="33" width="11.1796875" customWidth="1"/>
+    <col min="34" max="34" width="22.90625" customWidth="1"/>
+    <col min="35" max="35" width="15.1796875" customWidth="1"/>
+    <col min="36" max="36" width="14.08984375" customWidth="1"/>
     <col min="37" max="37" width="26" customWidth="1"/>
-    <col min="38" max="38" width="13.109375" style="1" customWidth="1"/>
-    <col min="39" max="39" width="19.21875" customWidth="1"/>
-    <col min="40" max="40" width="16.88671875" customWidth="1"/>
-    <col min="41" max="41" width="25.21875" customWidth="1"/>
-    <col min="42" max="42" width="12.6640625" customWidth="1"/>
-    <col min="43" max="43" width="6.5546875" customWidth="1"/>
-    <col min="44" max="44" width="19.33203125" customWidth="1"/>
-    <col min="45" max="45" width="19.109375" customWidth="1"/>
-    <col min="46" max="46" width="15.88671875" customWidth="1"/>
-    <col min="47" max="47" width="19.21875" customWidth="1"/>
-    <col min="48" max="48" width="23.44140625" customWidth="1"/>
-    <col min="49" max="49" width="14.6640625" customWidth="1"/>
-    <col min="50" max="50" width="23.109375" customWidth="1"/>
-    <col min="51" max="51" width="28.6640625" customWidth="1"/>
-    <col min="52" max="52" width="17.77734375" customWidth="1"/>
-    <col min="53" max="53" width="22.44140625" customWidth="1"/>
-    <col min="54" max="54" width="17.77734375" customWidth="1"/>
+    <col min="38" max="38" width="13.08984375" style="1" customWidth="1"/>
+    <col min="39" max="39" width="19.1796875" customWidth="1"/>
+    <col min="40" max="40" width="16.90625" customWidth="1"/>
+    <col min="41" max="41" width="25.1796875" customWidth="1"/>
+    <col min="42" max="42" width="12.6328125" customWidth="1"/>
+    <col min="43" max="43" width="6.54296875" customWidth="1"/>
+    <col min="44" max="44" width="19.36328125" customWidth="1"/>
+    <col min="45" max="45" width="19.08984375" customWidth="1"/>
+    <col min="46" max="46" width="15.90625" customWidth="1"/>
+    <col min="47" max="47" width="19.1796875" customWidth="1"/>
+    <col min="48" max="48" width="23.453125" customWidth="1"/>
+    <col min="49" max="49" width="14.6328125" customWidth="1"/>
+    <col min="50" max="50" width="23.08984375" customWidth="1"/>
+    <col min="51" max="51" width="28.6328125" customWidth="1"/>
+    <col min="52" max="52" width="17.81640625" customWidth="1"/>
+    <col min="53" max="53" width="22.453125" customWidth="1"/>
+    <col min="54" max="54" width="17.81640625" customWidth="1"/>
     <col min="55" max="55" width="18" customWidth="1"/>
-    <col min="56" max="56" width="13.109375" customWidth="1"/>
-    <col min="57" max="57" width="15.5546875" customWidth="1"/>
-    <col min="58" max="58" width="18.88671875" customWidth="1"/>
-    <col min="59" max="59" width="10.77734375" customWidth="1"/>
-    <col min="60" max="60" width="27.33203125" customWidth="1"/>
+    <col min="56" max="56" width="13.08984375" customWidth="1"/>
+    <col min="57" max="57" width="15.54296875" customWidth="1"/>
+    <col min="58" max="58" width="18.90625" customWidth="1"/>
+    <col min="59" max="59" width="10.81640625" customWidth="1"/>
+    <col min="60" max="60" width="27.36328125" customWidth="1"/>
     <col min="61" max="61" width="12" customWidth="1"/>
-    <col min="62" max="62" width="9.109375" customWidth="1"/>
-    <col min="63" max="63" width="15.5546875" customWidth="1"/>
-    <col min="64" max="64" width="10.77734375" customWidth="1"/>
-    <col min="65" max="65" width="9.77734375" customWidth="1"/>
-    <col min="66" max="66" width="11.33203125" customWidth="1"/>
-    <col min="67" max="67" width="14.21875" customWidth="1"/>
+    <col min="62" max="62" width="9.08984375" customWidth="1"/>
+    <col min="63" max="63" width="15.54296875" customWidth="1"/>
+    <col min="64" max="64" width="10.81640625" customWidth="1"/>
+    <col min="65" max="65" width="9.81640625" customWidth="1"/>
+    <col min="66" max="66" width="11.36328125" customWidth="1"/>
+    <col min="67" max="67" width="14.1796875" customWidth="1"/>
     <col min="68" max="68" width="17" customWidth="1"/>
-    <col min="69" max="69" width="16.33203125" customWidth="1"/>
-    <col min="70" max="70" width="12.5546875" customWidth="1"/>
-    <col min="71" max="71" width="21.6640625" customWidth="1"/>
-    <col min="72" max="72" width="12.21875" customWidth="1"/>
-    <col min="73" max="73" width="27.44140625" customWidth="1"/>
-    <col min="74" max="74" width="29.21875" customWidth="1"/>
-    <col min="75" max="75" width="8.44140625" customWidth="1"/>
-    <col min="76" max="76" width="26.88671875" customWidth="1"/>
-    <col min="77" max="77" width="22.33203125" customWidth="1"/>
+    <col min="69" max="69" width="16.36328125" customWidth="1"/>
+    <col min="70" max="70" width="12.54296875" customWidth="1"/>
+    <col min="71" max="71" width="21.6328125" customWidth="1"/>
+    <col min="72" max="72" width="12.1796875" customWidth="1"/>
+    <col min="73" max="73" width="27.453125" customWidth="1"/>
+    <col min="74" max="74" width="29.1796875" customWidth="1"/>
+    <col min="75" max="75" width="8.453125" customWidth="1"/>
+    <col min="76" max="76" width="26.90625" customWidth="1"/>
+    <col min="77" max="77" width="22.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:65" s="2" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1290,294 +1281,286 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="7"/>
+      <c r="C2" s="8"/>
+      <c r="D2" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="E2" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H2" s="11" t="s">
         <v>64</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>118</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>67</v>
       </c>
       <c r="I2" s="12">
         <v>919193394</v>
       </c>
       <c r="J2" s="12" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="K2" s="12" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L2" s="13">
         <f t="shared" ref="L2:L3" ca="1" si="0">TODAY()-7</f>
-        <v>45779</v>
+        <v>45785</v>
       </c>
       <c r="M2" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="N2" s="15" t="s">
         <v>67</v>
-      </c>
-      <c r="N2" s="15" t="s">
-        <v>70</v>
       </c>
       <c r="O2" s="12">
         <v>44</v>
       </c>
       <c r="P2" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q2" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="R2" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="S2" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="T2" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="U2" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="Q2" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="R2" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="S2" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="T2" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="U2" s="17" t="s">
-        <v>74</v>
-      </c>
       <c r="V2" s="12" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="W2" s="18">
         <f t="shared" ref="W2:W3" ca="1" si="1">TODAY()-7</f>
-        <v>45779</v>
+        <v>45785</v>
       </c>
       <c r="X2" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y2" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z2" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA2" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="Y2" s="19" t="s">
+      <c r="AB2" t="s">
         <v>76</v>
-      </c>
-      <c r="Z2" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="AA2" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>79</v>
       </c>
       <c r="AC2" s="22">
         <v>356</v>
       </c>
       <c r="AD2" s="23" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="AE2" s="14" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="AF2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AG2" s="24">
         <f ca="1">TODAY()+365</f>
-        <v>46151</v>
+        <v>46157</v>
       </c>
       <c r="AH2" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI2" s="25" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK2" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="AI2" s="25" t="s">
+      <c r="AL2" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AM2" s="26" t="s">
         <v>85</v>
-      </c>
-      <c r="AK2" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL2" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="AM2" s="26" t="s">
-        <v>88</v>
       </c>
       <c r="AN2" s="26">
         <f t="shared" ref="AN2:AN3" ca="1" si="2">TODAY()+7</f>
-        <v>45793</v>
+        <v>45799</v>
       </c>
       <c r="AO2" s="14" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="AP2" s="15" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="AQ2" s="16" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="AR2" s="24">
         <f t="shared" ref="AR2:AR3" ca="1" si="3">TODAY()+365</f>
-        <v>46151</v>
+        <v>46157</v>
       </c>
       <c r="AS2" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="AT2" t="s">
         <v>89</v>
-      </c>
-      <c r="AT2" t="s">
-        <v>92</v>
       </c>
       <c r="AU2" s="13">
         <v>29221</v>
       </c>
       <c r="AV2" s="28" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="AW2" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="AX2" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="AY2" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="AZ2" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="BA2" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="BB2" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="BC2" s="30" t="s">
         <v>93</v>
-      </c>
-      <c r="AX2" s="28" t="s">
-        <v>72</v>
-      </c>
-      <c r="AY2" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="AZ2" s="29" t="s">
-        <v>95</v>
-      </c>
-      <c r="BA2" s="28" t="s">
-        <v>67</v>
-      </c>
-      <c r="BB2" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="BC2" s="30" t="s">
-        <v>96</v>
       </c>
       <c r="BD2" s="31">
         <v>281000757380</v>
       </c>
       <c r="BE2" s="30" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="BF2" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="BG2" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="BH2" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="BI2" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="BG2" s="32" t="s">
+      <c r="BJ2" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="BH2" s="30" t="s">
+      <c r="BK2" s="30" t="s">
         <v>99</v>
-      </c>
-      <c r="BI2" s="30" t="s">
-        <v>100</v>
-      </c>
-      <c r="BJ2" s="30" t="s">
-        <v>101</v>
-      </c>
-      <c r="BK2" s="30" t="s">
-        <v>102</v>
       </c>
       <c r="BL2" s="30">
         <v>36526</v>
       </c>
       <c r="BM2" s="30" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
-    <row r="3" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="33" t="s">
-        <v>104</v>
-      </c>
-      <c r="B3" s="34" t="s">
-        <v>105</v>
-      </c>
-      <c r="C3" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3" s="34"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="H3" s="11" t="s">
         <v>64</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>67</v>
       </c>
       <c r="I3" s="12">
         <v>919193436</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L3" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>45779</v>
+        <v>45785</v>
       </c>
       <c r="M3" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="N3" s="15" t="s">
         <v>67</v>
-      </c>
-      <c r="N3" s="15" t="s">
-        <v>70</v>
       </c>
       <c r="O3" s="12">
         <v>44</v>
       </c>
       <c r="P3" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q3" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="R3" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="S3" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="T3" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="U3" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="Q3" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="R3" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="S3" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="T3" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="U3" s="15" t="s">
-        <v>74</v>
-      </c>
       <c r="V3" s="12" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="W3" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>45779</v>
+        <v>45785</v>
       </c>
       <c r="X3" s="12" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="Y3" s="19" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="Z3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="AA3" s="21" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="AB3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="AC3" s="22">
         <v>365</v>
@@ -1586,114 +1569,114 @@
         <v>100</v>
       </c>
       <c r="AE3" s="14" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="AF3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="AG3" s="35" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="AH3" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI3" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>109</v>
+      </c>
+      <c r="AK3" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="AI3" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>113</v>
-      </c>
-      <c r="AK3" s="12" t="s">
-        <v>86</v>
-      </c>
       <c r="AL3" s="16" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="AM3" s="26" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AN3" s="26">
         <f t="shared" ca="1" si="2"/>
-        <v>45793</v>
+        <v>45799</v>
       </c>
       <c r="AO3" s="14" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="AP3" s="15" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="AQ3" s="16" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="AR3" s="24">
         <f t="shared" ca="1" si="3"/>
-        <v>46151</v>
+        <v>46157</v>
       </c>
       <c r="AS3" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="AT3" t="s">
         <v>89</v>
-      </c>
-      <c r="AT3" t="s">
-        <v>92</v>
       </c>
       <c r="AU3" s="13">
         <v>29221</v>
       </c>
       <c r="AV3" s="28" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="AW3" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="AX3" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="AY3" s="28" t="s">
+        <v>91</v>
+      </c>
+      <c r="AZ3" s="29" t="s">
+        <v>92</v>
+      </c>
+      <c r="BA3" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="BB3" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="BC3" s="30" t="s">
         <v>93</v>
-      </c>
-      <c r="AX3" s="28" t="s">
-        <v>72</v>
-      </c>
-      <c r="AY3" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="AZ3" s="29" t="s">
-        <v>95</v>
-      </c>
-      <c r="BA3" s="28" t="s">
-        <v>67</v>
-      </c>
-      <c r="BB3" s="30" t="s">
-        <v>67</v>
-      </c>
-      <c r="BC3" s="30" t="s">
-        <v>96</v>
       </c>
       <c r="BD3" s="31">
         <v>281000757481</v>
       </c>
       <c r="BE3" s="30" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="BF3" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="BG3" s="32" t="s">
+        <v>111</v>
+      </c>
+      <c r="BH3" s="30" t="s">
+        <v>96</v>
+      </c>
+      <c r="BI3" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="BG3" s="32" t="s">
-        <v>115</v>
-      </c>
-      <c r="BH3" s="30" t="s">
-        <v>99</v>
-      </c>
-      <c r="BI3" s="30" t="s">
-        <v>100</v>
-      </c>
       <c r="BJ3" s="30" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="BK3" s="30" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="BL3" s="30">
         <v>36526</v>
       </c>
       <c r="BM3" s="30" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="33"/>
       <c r="B4" s="6"/>
       <c r="C4" s="8"/>
@@ -1754,7 +1737,7 @@
       <c r="BL4" s="30"/>
       <c r="BM4" s="30"/>
     </row>
-    <row r="5" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="33"/>
       <c r="B5" s="33"/>
       <c r="C5" s="8"/>
@@ -1816,7 +1799,7 @@
       <c r="BL5" s="30"/>
       <c r="BM5" s="30"/>
     </row>
-    <row r="6" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="33"/>
       <c r="B6" s="33"/>
       <c r="C6" s="8"/>
@@ -1878,7 +1861,7 @@
       <c r="BL6" s="30"/>
       <c r="BM6" s="30"/>
     </row>
-    <row r="7" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="33"/>
       <c r="B7" s="33"/>
       <c r="C7" s="8"/>
@@ -1939,7 +1922,7 @@
       <c r="BL7" s="30"/>
       <c r="BM7" s="30"/>
     </row>
-    <row r="8" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="33"/>
       <c r="B8" s="33"/>
       <c r="C8" s="8"/>
@@ -2000,7 +1983,7 @@
       <c r="BL8" s="30"/>
       <c r="BM8" s="30"/>
     </row>
-    <row r="9" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="33"/>
       <c r="B9" s="33"/>
       <c r="C9" s="8"/>
@@ -2062,7 +2045,7 @@
       <c r="BL9" s="30"/>
       <c r="BM9" s="30"/>
     </row>
-    <row r="10" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="33"/>
       <c r="B10" s="33"/>
       <c r="C10" s="8"/>
@@ -2123,7 +2106,7 @@
       <c r="BL10" s="30"/>
       <c r="BM10" s="30"/>
     </row>
-    <row r="11" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="33"/>
       <c r="B11" s="33"/>
       <c r="C11" s="8"/>
@@ -2184,7 +2167,7 @@
       <c r="BL11" s="30"/>
       <c r="BM11" s="30"/>
     </row>
-    <row r="12" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="33"/>
       <c r="B12" s="33"/>
       <c r="C12" s="8"/>
@@ -2246,7 +2229,7 @@
       <c r="BL12" s="30"/>
       <c r="BM12" s="30"/>
     </row>
-    <row r="13" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="33"/>
       <c r="B13" s="33"/>
       <c r="C13" s="8"/>
@@ -2309,7 +2292,7 @@
       <c r="BL13" s="30"/>
       <c r="BM13" s="30"/>
     </row>
-    <row r="14" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="33"/>
       <c r="B14" s="33"/>
       <c r="C14" s="8"/>
@@ -2376,7 +2359,7 @@
       <c r="BL14" s="30"/>
       <c r="BM14" s="30"/>
     </row>
-    <row r="15" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="33"/>
       <c r="B15" s="33"/>
       <c r="C15" s="8"/>
@@ -2438,7 +2421,7 @@
       <c r="BL15" s="30"/>
       <c r="BM15" s="30"/>
     </row>
-    <row r="16" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="33"/>
       <c r="B16" s="33"/>
       <c r="C16" s="8"/>
@@ -2500,9 +2483,9 @@
       <c r="BL16" s="30"/>
       <c r="BM16" s="30"/>
     </row>
-    <row r="17" spans="1:78" s="2" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" spans="1:78" s="2" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:78" s="2" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="18" spans="1:78" s="2" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="19" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -2582,7 +2565,7 @@
       <c r="BY19" s="2"/>
       <c r="BZ19" s="2"/>
     </row>
-    <row r="20" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -2662,7 +2645,7 @@
       <c r="BY20" s="2"/>
       <c r="BZ20" s="2"/>
     </row>
-    <row r="21" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -2742,7 +2725,7 @@
       <c r="BY21" s="2"/>
       <c r="BZ21" s="2"/>
     </row>
-    <row r="22" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -2822,7 +2805,7 @@
       <c r="BY22" s="2"/>
       <c r="BZ22" s="2"/>
     </row>
-    <row r="23" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -2902,7 +2885,7 @@
       <c r="BY23" s="2"/>
       <c r="BZ23" s="2"/>
     </row>
-    <row r="24" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -2982,7 +2965,7 @@
       <c r="BY24" s="2"/>
       <c r="BZ24" s="2"/>
     </row>
-    <row r="25" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -3062,7 +3045,7 @@
       <c r="BY25" s="2"/>
       <c r="BZ25" s="2"/>
     </row>
-    <row r="26" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -3142,7 +3125,7 @@
       <c r="BY26" s="2"/>
       <c r="BZ26" s="2"/>
     </row>
-    <row r="27" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -3222,7 +3205,7 @@
       <c r="BY27" s="2"/>
       <c r="BZ27" s="2"/>
     </row>
-    <row r="28" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -3302,7 +3285,7 @@
       <c r="BY28" s="2"/>
       <c r="BZ28" s="2"/>
     </row>
-    <row r="29" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -3382,7 +3365,7 @@
       <c r="BY29" s="2"/>
       <c r="BZ29" s="2"/>
     </row>
-    <row r="30" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -3462,7 +3445,7 @@
       <c r="BY30" s="2"/>
       <c r="BZ30" s="2"/>
     </row>
-    <row r="31" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -3542,7 +3525,7 @@
       <c r="BY31" s="2"/>
       <c r="BZ31" s="2"/>
     </row>
-    <row r="32" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -3622,7 +3605,7 @@
       <c r="BY32" s="2"/>
       <c r="BZ32" s="2"/>
     </row>
-    <row r="33" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -3702,7 +3685,7 @@
       <c r="BY33" s="2"/>
       <c r="BZ33" s="2"/>
     </row>
-    <row r="34" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -3782,7 +3765,7 @@
       <c r="BY34" s="2"/>
       <c r="BZ34" s="2"/>
     </row>
-    <row r="35" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -3862,7 +3845,7 @@
       <c r="BY35" s="2"/>
       <c r="BZ35" s="2"/>
     </row>
-    <row r="36" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -3942,7 +3925,7 @@
       <c r="BY36" s="2"/>
       <c r="BZ36" s="2"/>
     </row>
-    <row r="37" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -4022,7 +4005,7 @@
       <c r="BY37" s="2"/>
       <c r="BZ37" s="2"/>
     </row>
-    <row r="38" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -4102,7 +4085,7 @@
       <c r="BY38" s="2"/>
       <c r="BZ38" s="2"/>
     </row>
-    <row r="39" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -4182,7 +4165,7 @@
       <c r="BY39" s="2"/>
       <c r="BZ39" s="2"/>
     </row>
-    <row r="40" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -4262,7 +4245,7 @@
       <c r="BY40" s="2"/>
       <c r="BZ40" s="2"/>
     </row>
-    <row r="41" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -4342,7 +4325,7 @@
       <c r="BY41" s="2"/>
       <c r="BZ41" s="2"/>
     </row>
-    <row r="42" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -4422,7 +4405,7 @@
       <c r="BY42" s="2"/>
       <c r="BZ42" s="2"/>
     </row>
-    <row r="43" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -4502,7 +4485,7 @@
       <c r="BY43" s="2"/>
       <c r="BZ43" s="2"/>
     </row>
-    <row r="44" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -4582,7 +4565,7 @@
       <c r="BY44" s="2"/>
       <c r="BZ44" s="2"/>
     </row>
-    <row r="45" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -4662,7 +4645,7 @@
       <c r="BY45" s="2"/>
       <c r="BZ45" s="2"/>
     </row>
-    <row r="46" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -4742,7 +4725,7 @@
       <c r="BY46" s="2"/>
       <c r="BZ46" s="2"/>
     </row>
-    <row r="47" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -4822,7 +4805,7 @@
       <c r="BY47" s="2"/>
       <c r="BZ47" s="2"/>
     </row>
-    <row r="48" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -4902,7 +4885,7 @@
       <c r="BY48" s="2"/>
       <c r="BZ48" s="2"/>
     </row>
-    <row r="49" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -4982,7 +4965,7 @@
       <c r="BY49" s="2"/>
       <c r="BZ49" s="2"/>
     </row>
-    <row r="50" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -5062,7 +5045,7 @@
       <c r="BY50" s="2"/>
       <c r="BZ50" s="2"/>
     </row>
-    <row r="51" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -5142,7 +5125,7 @@
       <c r="BY51" s="2"/>
       <c r="BZ51" s="2"/>
     </row>
-    <row r="52" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -5222,7 +5205,7 @@
       <c r="BY52" s="2"/>
       <c r="BZ52" s="2"/>
     </row>
-    <row r="53" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -5302,7 +5285,7 @@
       <c r="BY53" s="2"/>
       <c r="BZ53" s="2"/>
     </row>
-    <row r="54" spans="1:78" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:78" ht="14.5" x14ac:dyDescent="0.35">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>

--- a/Data/Hires/Workday_NewHire_Spain_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Spain_Regression_PK17.xlsx
@@ -1,37 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6162A306-448A-42BC-8CC8-123B2B3076D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="7360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="7360"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">Sheet1!$A$1:$BY$53</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="121">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -222,9 +208,441 @@
     <t>Test_1</t>
   </si>
   <si>
+    <t xml:space="preserve">Test failed for 'Tyree Davis' Employee:{undefined}TimeoutError: locator.click: Timeout 30000ms exceeded.
+Call log:
+  [2m- waiting for getByLabel('My Tasks Items')[22m
+[2m  -   locator resolved to &lt;button class="wdappchrome-w" data-automation-id="inbox_…&gt;…&lt;/button&gt;[22m
+[2m  - attempting click action[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #1[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #2[22m
+[2m  -   waiting 20ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #3[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #4[22m
+[2m  -   waiting 100ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #5[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #6[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #7[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #8[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #9[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #10[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #11[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #12[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #13[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #14[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #15[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #16[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #17[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #18[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #19[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #20[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #21[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #22[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #23[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #24[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #25[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #26[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #27[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #28[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #29[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #30[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #31[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #32[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #33[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #34[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #35[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #36[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #37[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #38[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #39[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #40[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #41[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #42[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #43[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #44[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #45[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #46[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #47[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #48[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #49[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #50[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #51[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #52[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #53[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #54[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #55[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #56[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #57[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #58[22m
+[2m  -   waiting 500ms[22m
+[2m  -   waiting for element to be visible, enabled and stable[22m
+[2m  -   element is visible, enabled and stable[22m
+[2m  -   scrolling into view if needed[22m
+[2m  -   done scrolling[22m
+[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
+[2m  - retrying click action, attempt #59[22m
+[2m  -   waiting 500ms[22m
+</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
     <t>356 Recruitment (Posob Zujefy Pyronu (2577) (Inherited))</t>
   </si>
   <si>
+    <t>Tyree</t>
+  </si>
+  <si>
+    <t>Davis</t>
+  </si>
+  <si>
+    <t>SLNameOne</t>
+  </si>
+  <si>
     <t>Spain</t>
   </si>
   <si>
@@ -339,10 +757,19 @@
     <t>Test_2</t>
   </si>
   <si>
+    <t>Test failed for 'Waldo Schinner' Employee: Errors and AlertsAlertsNational IDs (Row 1)This national identifier you entered is already in use. Verify that the information is accurate.National IDs (Row 1)Verify that you entered the correct ID. The value you entered failed our validation test.National IDs (Row 2)This national identifier you entered is already in use. Verify that the information is accurate.National IDs (Row 2)Verify that you entered the correct ID. The value you entered failed our validation test. &amp; find failed Screenshot Path:-&gt;H:\WDplaywright_LatestCode/WorkdayFailedScreenshot/2025-05-15T21-27-06-805Z.png</t>
+  </si>
+  <si>
     <t>365 Store Management (Cisuw Hapagu Pahame (10274587))</t>
   </si>
   <si>
-    <t>Auto 87795665</t>
+    <t>Waldo</t>
+  </si>
+  <si>
+    <t>Schinner</t>
+  </si>
+  <si>
+    <t>Auto 87179098</t>
   </si>
   <si>
     <t>Permanent</t>
@@ -371,124 +798,109 @@
   </si>
   <si>
     <t>54 - ENSEÑANZAS UNIVERSITARIAS DE PRIMER CICLO Y EQUIVALENTES</t>
-  </si>
-  <si>
-    <t>Tyree</t>
-  </si>
-  <si>
-    <t>Davis</t>
-  </si>
-  <si>
-    <t>Waldo</t>
-  </si>
-  <si>
-    <t>Schinner</t>
-  </si>
-  <si>
-    <t>SLNameOne</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
+      <sz val="10"/>
+      <name val="Calibri Light"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
+      <sz val="10"/>
+      <name val="Calibri Light"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <color theme="1"/>
+      <family val="2"/>
       <sz val="14"/>
-      <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10"/>
       <color indexed="8"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <color theme="1"/>
+      <family val="2"/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Segoe UI"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <color rgb="FFFF0000"/>
+      <family val="2"/>
       <sz val="14"/>
-      <color rgb="FFFF0000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -514,18 +926,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
+        <fgColor theme="4" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -539,18 +946,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -560,12 +959,8 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -589,13 +984,13 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -621,7 +1016,7 @@
     <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
@@ -644,7 +1039,7 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -675,7 +1070,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -695,7 +1090,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
@@ -708,7 +1103,7 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1002,9 +1397,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BZ54"/>
-  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.36328125" customWidth="1"/>
     <col min="2" max="2" width="11.08984375" customWidth="1"/>
@@ -1084,7 +1479,7 @@
     <col min="77" max="77" width="22.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:65" s="2" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="1" ht="14.5" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1281,286 +1676,294 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="8"/>
+      <c r="B2" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>64</v>
+      </c>
       <c r="D2" s="9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>113</v>
+        <v>66</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>114</v>
+        <v>67</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="I2" s="12">
         <v>919193394</v>
       </c>
       <c r="J2" s="12" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="K2" s="12" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="L2" s="13">
-        <f t="shared" ref="L2:L3" ca="1" si="0">TODAY()-7</f>
+        <f t="shared" ref="L2:L3" si="0">TODAY()-7</f>
         <v>45785</v>
       </c>
       <c r="M2" s="14" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="N2" s="15" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="O2" s="12">
         <v>44</v>
       </c>
       <c r="P2" s="12" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="Q2" s="15" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="R2" s="12" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="S2" s="12" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="T2" s="16" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="U2" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="V2" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="V2" s="12" t="s">
-        <v>66</v>
-      </c>
       <c r="W2" s="18">
-        <f t="shared" ref="W2:W3" ca="1" si="1">TODAY()-7</f>
+        <f t="shared" ref="W2:W3" si="1">TODAY()-7</f>
         <v>45785</v>
       </c>
       <c r="X2" s="12" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="Y2" s="19" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="Z2" s="20" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AA2" s="21" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AB2" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AC2" s="22">
         <v>356</v>
       </c>
       <c r="AD2" s="23" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="AE2" s="14" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="AF2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AG2" s="24">
-        <f ca="1">TODAY()+365</f>
+        <f>TODAY()+365</f>
         <v>46157</v>
       </c>
       <c r="AH2" s="12" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AI2" s="25" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="AJ2" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="AK2" s="12" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="AL2" s="16" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="AM2" s="26" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN2" s="26">
-        <f t="shared" ref="AN2:AN3" ca="1" si="2">TODAY()+7</f>
+        <f t="shared" ref="AN2:AN3" si="2">TODAY()+7</f>
         <v>45799</v>
       </c>
       <c r="AO2" s="14" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="AP2" s="15" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="AQ2" s="16" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="AR2" s="24">
-        <f t="shared" ref="AR2:AR3" ca="1" si="3">TODAY()+365</f>
+        <f t="shared" ref="AR2:AR3" si="3">TODAY()+365</f>
         <v>46157</v>
       </c>
       <c r="AS2" s="27" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="AT2" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="AU2" s="13">
         <v>29221</v>
       </c>
       <c r="AV2" s="28" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="AW2" s="28" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AX2" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="AY2" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="AZ2" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="BA2" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="AY2" s="28" t="s">
-        <v>91</v>
-      </c>
-      <c r="AZ2" s="29" t="s">
-        <v>92</v>
-      </c>
-      <c r="BA2" s="28" t="s">
-        <v>64</v>
-      </c>
       <c r="BB2" s="30" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="BC2" s="30" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="BD2" s="31">
         <v>281000757380</v>
       </c>
       <c r="BE2" s="30" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="BF2" s="30" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="BG2" s="32" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BH2" s="30" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="BI2" s="30" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="BJ2" s="30" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="BK2" s="30" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="BL2" s="30">
         <v>36526</v>
       </c>
       <c r="BM2" s="30" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
-    <row r="3" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="33" t="s">
-        <v>101</v>
-      </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="8"/>
+        <v>106</v>
+      </c>
+      <c r="B3" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>64</v>
+      </c>
       <c r="D3" s="9" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="I3" s="12">
         <v>919193436</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="L3" s="13">
-        <f t="shared" ca="1" si="0"/>
+        <f t="shared" si="0"/>
         <v>45785</v>
       </c>
       <c r="M3" s="14" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="O3" s="12">
         <v>44</v>
       </c>
       <c r="P3" s="12" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="Q3" s="15" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="R3" s="12" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="S3" s="12" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="T3" s="16" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="U3" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="V3" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="V3" s="12" t="s">
-        <v>66</v>
-      </c>
       <c r="W3" s="18">
-        <f t="shared" ca="1" si="1"/>
+        <f t="shared" si="1"/>
         <v>45785</v>
       </c>
       <c r="X3" s="12" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="Y3" s="19" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="Z3" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="AA3" s="21" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="AB3" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="AC3" s="22">
         <v>365</v>
@@ -1569,114 +1972,114 @@
         <v>100</v>
       </c>
       <c r="AE3" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>115</v>
+      </c>
+      <c r="AG3" s="35" t="s">
         <v>78</v>
       </c>
-      <c r="AF3" t="s">
-        <v>107</v>
-      </c>
-      <c r="AG3" s="35" t="s">
-        <v>73</v>
-      </c>
       <c r="AH3" s="12" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AI3" s="25" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="AJ3" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="AK3" s="12" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="AL3" s="16" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="AM3" s="26" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN3" s="26">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" si="2"/>
         <v>45799</v>
       </c>
       <c r="AO3" s="14" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="AP3" s="15" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="AQ3" s="16" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="AR3" s="24">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" si="3"/>
         <v>46157</v>
       </c>
       <c r="AS3" s="27" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="AT3" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="AU3" s="13">
         <v>29221</v>
       </c>
       <c r="AV3" s="28" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="AW3" s="28" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AX3" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="AY3" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="AZ3" s="29" t="s">
+        <v>97</v>
+      </c>
+      <c r="BA3" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="AY3" s="28" t="s">
-        <v>91</v>
-      </c>
-      <c r="AZ3" s="29" t="s">
-        <v>92</v>
-      </c>
-      <c r="BA3" s="28" t="s">
-        <v>64</v>
-      </c>
       <c r="BB3" s="30" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="BC3" s="30" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="BD3" s="31">
         <v>281000757481</v>
       </c>
       <c r="BE3" s="30" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="BF3" s="30" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="BG3" s="32" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="BH3" s="30" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="BI3" s="30" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="BJ3" s="30" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="BK3" s="30" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="BL3" s="30">
         <v>36526</v>
       </c>
       <c r="BM3" s="30" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
     </row>
-    <row r="4" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="33"/>
       <c r="B4" s="6"/>
       <c r="C4" s="8"/>
@@ -1737,7 +2140,7 @@
       <c r="BL4" s="30"/>
       <c r="BM4" s="30"/>
     </row>
-    <row r="5" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="33"/>
       <c r="B5" s="33"/>
       <c r="C5" s="8"/>
@@ -1799,7 +2202,7 @@
       <c r="BL5" s="30"/>
       <c r="BM5" s="30"/>
     </row>
-    <row r="6" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="33"/>
       <c r="B6" s="33"/>
       <c r="C6" s="8"/>
@@ -1861,7 +2264,7 @@
       <c r="BL6" s="30"/>
       <c r="BM6" s="30"/>
     </row>
-    <row r="7" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="33"/>
       <c r="B7" s="33"/>
       <c r="C7" s="8"/>
@@ -1922,7 +2325,7 @@
       <c r="BL7" s="30"/>
       <c r="BM7" s="30"/>
     </row>
-    <row r="8" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="33"/>
       <c r="B8" s="33"/>
       <c r="C8" s="8"/>
@@ -1983,7 +2386,7 @@
       <c r="BL8" s="30"/>
       <c r="BM8" s="30"/>
     </row>
-    <row r="9" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="33"/>
       <c r="B9" s="33"/>
       <c r="C9" s="8"/>
@@ -2045,7 +2448,7 @@
       <c r="BL9" s="30"/>
       <c r="BM9" s="30"/>
     </row>
-    <row r="10" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="33"/>
       <c r="B10" s="33"/>
       <c r="C10" s="8"/>
@@ -2106,7 +2509,7 @@
       <c r="BL10" s="30"/>
       <c r="BM10" s="30"/>
     </row>
-    <row r="11" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="33"/>
       <c r="B11" s="33"/>
       <c r="C11" s="8"/>
@@ -2167,7 +2570,7 @@
       <c r="BL11" s="30"/>
       <c r="BM11" s="30"/>
     </row>
-    <row r="12" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="33"/>
       <c r="B12" s="33"/>
       <c r="C12" s="8"/>
@@ -2229,7 +2632,7 @@
       <c r="BL12" s="30"/>
       <c r="BM12" s="30"/>
     </row>
-    <row r="13" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="33"/>
       <c r="B13" s="33"/>
       <c r="C13" s="8"/>
@@ -2292,7 +2695,7 @@
       <c r="BL13" s="30"/>
       <c r="BM13" s="30"/>
     </row>
-    <row r="14" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="33"/>
       <c r="B14" s="33"/>
       <c r="C14" s="8"/>
@@ -2359,7 +2762,7 @@
       <c r="BL14" s="30"/>
       <c r="BM14" s="30"/>
     </row>
-    <row r="15" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="33"/>
       <c r="B15" s="33"/>
       <c r="C15" s="8"/>
@@ -2421,7 +2824,7 @@
       <c r="BL15" s="30"/>
       <c r="BM15" s="30"/>
     </row>
-    <row r="16" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="33"/>
       <c r="B16" s="33"/>
       <c r="C16" s="8"/>
@@ -2483,9 +2886,9 @@
       <c r="BL16" s="30"/>
       <c r="BM16" s="30"/>
     </row>
-    <row r="17" spans="1:78" s="2" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="1:78" s="2" customFormat="1" ht="13.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="17" ht="13.75" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="18" ht="13.75" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="19" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -2565,7 +2968,7 @@
       <c r="BY19" s="2"/>
       <c r="BZ19" s="2"/>
     </row>
-    <row r="20" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="20" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -2645,7 +3048,7 @@
       <c r="BY20" s="2"/>
       <c r="BZ20" s="2"/>
     </row>
-    <row r="21" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="21" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -2725,7 +3128,7 @@
       <c r="BY21" s="2"/>
       <c r="BZ21" s="2"/>
     </row>
-    <row r="22" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="22" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -2805,7 +3208,7 @@
       <c r="BY22" s="2"/>
       <c r="BZ22" s="2"/>
     </row>
-    <row r="23" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="23" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -2885,7 +3288,7 @@
       <c r="BY23" s="2"/>
       <c r="BZ23" s="2"/>
     </row>
-    <row r="24" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="24" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -2965,7 +3368,7 @@
       <c r="BY24" s="2"/>
       <c r="BZ24" s="2"/>
     </row>
-    <row r="25" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="25" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -3045,7 +3448,7 @@
       <c r="BY25" s="2"/>
       <c r="BZ25" s="2"/>
     </row>
-    <row r="26" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="26" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -3125,7 +3528,7 @@
       <c r="BY26" s="2"/>
       <c r="BZ26" s="2"/>
     </row>
-    <row r="27" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="27" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -3205,7 +3608,7 @@
       <c r="BY27" s="2"/>
       <c r="BZ27" s="2"/>
     </row>
-    <row r="28" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="28" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -3285,7 +3688,7 @@
       <c r="BY28" s="2"/>
       <c r="BZ28" s="2"/>
     </row>
-    <row r="29" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="29" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -3365,7 +3768,7 @@
       <c r="BY29" s="2"/>
       <c r="BZ29" s="2"/>
     </row>
-    <row r="30" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="30" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -3445,7 +3848,7 @@
       <c r="BY30" s="2"/>
       <c r="BZ30" s="2"/>
     </row>
-    <row r="31" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="31" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -3525,7 +3928,7 @@
       <c r="BY31" s="2"/>
       <c r="BZ31" s="2"/>
     </row>
-    <row r="32" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="32" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -3605,7 +4008,7 @@
       <c r="BY32" s="2"/>
       <c r="BZ32" s="2"/>
     </row>
-    <row r="33" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="33" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -3685,7 +4088,7 @@
       <c r="BY33" s="2"/>
       <c r="BZ33" s="2"/>
     </row>
-    <row r="34" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="34" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -3765,7 +4168,7 @@
       <c r="BY34" s="2"/>
       <c r="BZ34" s="2"/>
     </row>
-    <row r="35" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="35" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -3845,7 +4248,7 @@
       <c r="BY35" s="2"/>
       <c r="BZ35" s="2"/>
     </row>
-    <row r="36" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="36" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -3925,7 +4328,7 @@
       <c r="BY36" s="2"/>
       <c r="BZ36" s="2"/>
     </row>
-    <row r="37" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="37" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -4005,7 +4408,7 @@
       <c r="BY37" s="2"/>
       <c r="BZ37" s="2"/>
     </row>
-    <row r="38" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="38" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -4085,7 +4488,7 @@
       <c r="BY38" s="2"/>
       <c r="BZ38" s="2"/>
     </row>
-    <row r="39" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="39" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -4165,7 +4568,7 @@
       <c r="BY39" s="2"/>
       <c r="BZ39" s="2"/>
     </row>
-    <row r="40" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="40" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -4245,7 +4648,7 @@
       <c r="BY40" s="2"/>
       <c r="BZ40" s="2"/>
     </row>
-    <row r="41" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="41" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -4325,7 +4728,7 @@
       <c r="BY41" s="2"/>
       <c r="BZ41" s="2"/>
     </row>
-    <row r="42" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="42" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -4405,7 +4808,7 @@
       <c r="BY42" s="2"/>
       <c r="BZ42" s="2"/>
     </row>
-    <row r="43" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="43" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -4485,7 +4888,7 @@
       <c r="BY43" s="2"/>
       <c r="BZ43" s="2"/>
     </row>
-    <row r="44" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="44" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -4565,7 +4968,7 @@
       <c r="BY44" s="2"/>
       <c r="BZ44" s="2"/>
     </row>
-    <row r="45" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="45" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -4645,7 +5048,7 @@
       <c r="BY45" s="2"/>
       <c r="BZ45" s="2"/>
     </row>
-    <row r="46" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="46" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -4725,7 +5128,7 @@
       <c r="BY46" s="2"/>
       <c r="BZ46" s="2"/>
     </row>
-    <row r="47" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="47" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -4805,7 +5208,7 @@
       <c r="BY47" s="2"/>
       <c r="BZ47" s="2"/>
     </row>
-    <row r="48" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="48" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -4885,7 +5288,7 @@
       <c r="BY48" s="2"/>
       <c r="BZ48" s="2"/>
     </row>
-    <row r="49" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="49" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -4965,7 +5368,7 @@
       <c r="BY49" s="2"/>
       <c r="BZ49" s="2"/>
     </row>
-    <row r="50" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="50" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -5045,7 +5448,7 @@
       <c r="BY50" s="2"/>
       <c r="BZ50" s="2"/>
     </row>
-    <row r="51" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="51" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -5125,7 +5528,7 @@
       <c r="BY51" s="2"/>
       <c r="BZ51" s="2"/>
     </row>
-    <row r="52" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="52" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -5205,7 +5608,7 @@
       <c r="BY52" s="2"/>
       <c r="BZ52" s="2"/>
     </row>
-    <row r="53" spans="1:78" s="38" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="53" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -5285,7 +5688,7 @@
       <c r="BY53" s="2"/>
       <c r="BZ53" s="2"/>
     </row>
-    <row r="54" spans="1:78" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="54" ht="14.5" customHeight="1" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -5366,18 +5769,66 @@
       <c r="BZ54" s="2"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AM10:AM16 X10:X16 V10:V16 R10:S16 J10:K16 BI10:BI16 BC10:BC16 AY10:AY16 AP10:AP16" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="18">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AM10:AM16">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AM2:AM16 X2:X16 V2:V16 R2:S16 J2:K16 BI2:BI16 BC2:BC16 AY2:AY16 AP2:AP16" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AM2:AM16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AP10:AP16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AP2:AP16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY10:AY16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY2:AY16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC10:BC16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC2:BC16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BI10:BI16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BI2:BI16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J10:K16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:K16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R10:S16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:S16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V10:V16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X10:X16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X16">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="U2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="U2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId2"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/Data/Hires/Workday_NewHire_Spain_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Spain_Regression_PK17.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="7360"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="121">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -208,436 +208,19 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t xml:space="preserve">Test failed for 'Tyree Davis' Employee:{undefined}TimeoutError: locator.click: Timeout 30000ms exceeded.
-Call log:
-  [2m- waiting for getByLabel('My Tasks Items')[22m
-[2m  -   locator resolved to &lt;button class="wdappchrome-w" data-automation-id="inbox_…&gt;…&lt;/button&gt;[22m
-[2m  - attempting click action[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #1[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #2[22m
-[2m  -   waiting 20ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #3[22m
-[2m  -   waiting 100ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #4[22m
-[2m  -   waiting 100ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #5[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #6[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #7[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #8[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #9[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #10[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #11[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #12[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #13[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #14[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #15[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #16[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #17[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #18[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #19[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #20[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #21[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #22[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #23[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #24[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #25[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #26[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #27[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #28[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #29[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #30[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #31[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #32[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #33[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #34[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #35[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #36[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #37[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #38[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #39[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #40[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #41[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #42[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #43[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #44[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #45[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #46[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #47[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #48[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #49[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #50[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #51[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #52[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #53[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #54[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #55[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #56[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #57[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #58[22m
-[2m  -   waiting 500ms[22m
-[2m  -   waiting for element to be visible, enabled and stable[22m
-[2m  -   element is visible, enabled and stable[22m
-[2m  -   scrolling into view if needed[22m
-[2m  -   done scrolling[22m
-[2m  -   &lt;div class="WNMP" data-automation-id="modalOverlay"&gt;…&lt;/div&gt; from &lt;div id="content-container"&gt;…&lt;/div&gt; subtree intercepts pointer events[22m
-[2m  - retrying click action, attempt #59[22m
-[2m  -   waiting 500ms[22m
-</t>
-  </si>
-  <si>
-    <t>Failed</t>
+    <t>10699543</t>
+  </si>
+  <si>
+    <t>Passed</t>
   </si>
   <si>
     <t>356 Recruitment (Posob Zujefy Pyronu (2577) (Inherited))</t>
   </si>
   <si>
-    <t>Tyree</t>
-  </si>
-  <si>
-    <t>Davis</t>
+    <t>Mrs</t>
+  </si>
+  <si>
+    <t>GSKSKk</t>
   </si>
   <si>
     <t>SLNameOne</t>
@@ -736,7 +319,7 @@
     <t>ID Card (DNI) Number</t>
   </si>
   <si>
-    <t>10006465A</t>
+    <t>10006501A</t>
   </si>
   <si>
     <t>BBVAESMM111</t>
@@ -757,19 +340,19 @@
     <t>Test_2</t>
   </si>
   <si>
-    <t>Test failed for 'Waldo Schinner' Employee: Errors and AlertsAlertsNational IDs (Row 1)This national identifier you entered is already in use. Verify that the information is accurate.National IDs (Row 1)Verify that you entered the correct ID. The value you entered failed our validation test.National IDs (Row 2)This national identifier you entered is already in use. Verify that the information is accurate.National IDs (Row 2)Verify that you entered the correct ID. The value you entered failed our validation test. &amp; find failed Screenshot Path:-&gt;H:\WDplaywright_LatestCode/WorkdayFailedScreenshot/2025-05-15T21-27-06-805Z.png</t>
+    <t>10699544</t>
   </si>
   <si>
     <t>365 Store Management (Cisuw Hapagu Pahame (10274587))</t>
   </si>
   <si>
-    <t>Waldo</t>
-  </si>
-  <si>
-    <t>Schinner</t>
-  </si>
-  <si>
-    <t>Auto 87179098</t>
+    <t>SchirRR</t>
+  </si>
+  <si>
+    <t>SLNameTwoo</t>
+  </si>
+  <si>
+    <t>Auto 28086090</t>
   </si>
   <si>
     <t>Permanent</t>
@@ -794,7 +377,7 @@
 </t>
   </si>
   <si>
-    <t>10006466A</t>
+    <t>10006502A</t>
   </si>
   <si>
     <t>54 - ENSEÑANZAS UNIVERSITARIAS DE PRIMER CICLO Y EQUIVALENTES</t>
@@ -900,7 +483,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -922,6 +505,11 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FF00"/>
       </patternFill>
     </fill>
     <fill>
@@ -967,7 +555,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -982,15 +570,15 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1016,7 +604,7 @@
     <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
@@ -1039,7 +627,7 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1063,6 +651,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1070,7 +661,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1090,7 +681,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
@@ -1103,7 +694,7 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1711,8 +1302,8 @@
         <v>71</v>
       </c>
       <c r="L2" s="13">
-        <f t="shared" ref="L2:L3" si="0">TODAY()-7</f>
-        <v>45785</v>
+        <f t="shared" ref="L2" si="0">TODAY()-7</f>
+        <v>45803</v>
       </c>
       <c r="M2" s="14" t="s">
         <v>69</v>
@@ -1745,8 +1336,8 @@
         <v>71</v>
       </c>
       <c r="W2" s="18">
-        <f t="shared" ref="W2:W3" si="1">TODAY()-7</f>
-        <v>45785</v>
+        <f t="shared" ref="W2" si="1">TODAY()-7</f>
+        <v>45803</v>
       </c>
       <c r="X2" s="12" t="s">
         <v>77</v>
@@ -1777,7 +1368,7 @@
       </c>
       <c r="AG2" s="24">
         <f>TODAY()+365</f>
-        <v>46157</v>
+        <v>46175</v>
       </c>
       <c r="AH2" s="12" t="s">
         <v>85</v>
@@ -1798,8 +1389,8 @@
         <v>90</v>
       </c>
       <c r="AN2" s="26">
-        <f t="shared" ref="AN2:AN3" si="2">TODAY()+7</f>
-        <v>45799</v>
+        <f t="shared" ref="AN2" si="2">TODAY()+7</f>
+        <v>45817</v>
       </c>
       <c r="AO2" s="14" t="s">
         <v>91</v>
@@ -1811,8 +1402,8 @@
         <v>93</v>
       </c>
       <c r="AR2" s="24">
-        <f t="shared" ref="AR2:AR3" si="3">TODAY()+365</f>
-        <v>46157</v>
+        <f t="shared" ref="AR2" si="3">TODAY()+365</f>
+        <v>46175</v>
       </c>
       <c r="AS2" s="27" t="s">
         <v>91</v>
@@ -1848,7 +1439,7 @@
         <v>98</v>
       </c>
       <c r="BD2" s="31">
-        <v>281000757380</v>
+        <v>281000757497</v>
       </c>
       <c r="BE2" s="30" t="s">
         <v>69</v>
@@ -1892,13 +1483,13 @@
         <v>108</v>
       </c>
       <c r="E3" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="F3" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="G3" s="10" t="s">
         <v>110</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>68</v>
       </c>
       <c r="H3" s="11" t="s">
         <v>69</v>
@@ -1913,8 +1504,7 @@
         <v>71</v>
       </c>
       <c r="L3" s="13">
-        <f t="shared" si="0"/>
-        <v>45785</v>
+        <v>45800</v>
       </c>
       <c r="M3" s="14" t="s">
         <v>69</v>
@@ -1925,8 +1515,8 @@
       <c r="O3" s="12">
         <v>44</v>
       </c>
-      <c r="P3" s="12" t="s">
-        <v>73</v>
+      <c r="P3" s="12">
+        <v>28013</v>
       </c>
       <c r="Q3" s="15" t="s">
         <v>74</v>
@@ -1947,8 +1537,7 @@
         <v>71</v>
       </c>
       <c r="W3" s="18">
-        <f t="shared" si="1"/>
-        <v>45785</v>
+        <v>45800</v>
       </c>
       <c r="X3" s="12" t="s">
         <v>77</v>
@@ -1992,15 +1581,14 @@
       <c r="AK3" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="AL3" s="16" t="s">
+      <c r="AL3" s="36" t="s">
         <v>118</v>
       </c>
       <c r="AM3" s="26" t="s">
         <v>90</v>
       </c>
       <c r="AN3" s="26">
-        <f t="shared" si="2"/>
-        <v>45799</v>
+        <v>45814</v>
       </c>
       <c r="AO3" s="14" t="s">
         <v>91</v>
@@ -2012,8 +1600,7 @@
         <v>93</v>
       </c>
       <c r="AR3" s="24">
-        <f t="shared" si="3"/>
-        <v>46157</v>
+        <v>46172</v>
       </c>
       <c r="AS3" s="27" t="s">
         <v>91</v>
@@ -2036,8 +1623,8 @@
       <c r="AY3" s="28" t="s">
         <v>96</v>
       </c>
-      <c r="AZ3" s="29" t="s">
-        <v>97</v>
+      <c r="AZ3" s="29">
+        <v>40844</v>
       </c>
       <c r="BA3" s="28" t="s">
         <v>69</v>
@@ -2049,7 +1636,7 @@
         <v>98</v>
       </c>
       <c r="BD3" s="31">
-        <v>281000757481</v>
+        <v>281000757498</v>
       </c>
       <c r="BE3" s="30" t="s">
         <v>69</v>
@@ -2085,7 +1672,7 @@
       <c r="C4" s="8"/>
       <c r="D4" s="9"/>
       <c r="E4" s="10"/>
-      <c r="F4" s="36"/>
+      <c r="F4" s="37"/>
       <c r="G4" s="10"/>
       <c r="H4" s="11"/>
       <c r="I4" s="12"/>
@@ -2146,7 +1733,7 @@
       <c r="C5" s="8"/>
       <c r="D5" s="9"/>
       <c r="E5" s="10"/>
-      <c r="F5" s="36"/>
+      <c r="F5" s="37"/>
       <c r="G5" s="10"/>
       <c r="H5" s="11"/>
       <c r="I5" s="12"/>
@@ -2208,7 +1795,7 @@
       <c r="C6" s="8"/>
       <c r="D6" s="9"/>
       <c r="E6" s="10"/>
-      <c r="F6" s="36"/>
+      <c r="F6" s="37"/>
       <c r="G6" s="10"/>
       <c r="H6" s="11"/>
       <c r="I6" s="12"/>
@@ -2270,7 +1857,7 @@
       <c r="C7" s="8"/>
       <c r="D7" s="9"/>
       <c r="E7" s="10"/>
-      <c r="F7" s="36"/>
+      <c r="F7" s="37"/>
       <c r="G7" s="10"/>
       <c r="H7" s="11"/>
       <c r="I7" s="12"/>
@@ -2331,7 +1918,7 @@
       <c r="C8" s="8"/>
       <c r="D8" s="9"/>
       <c r="E8" s="10"/>
-      <c r="F8" s="36"/>
+      <c r="F8" s="37"/>
       <c r="G8" s="10"/>
       <c r="H8" s="11"/>
       <c r="I8" s="12"/>
@@ -2392,7 +1979,7 @@
       <c r="C9" s="8"/>
       <c r="D9" s="9"/>
       <c r="E9" s="10"/>
-      <c r="F9" s="36"/>
+      <c r="F9" s="37"/>
       <c r="G9" s="10"/>
       <c r="H9" s="11"/>
       <c r="I9" s="12"/>
@@ -2454,7 +2041,7 @@
       <c r="C10" s="8"/>
       <c r="D10" s="9"/>
       <c r="E10" s="10"/>
-      <c r="F10" s="36"/>
+      <c r="F10" s="37"/>
       <c r="G10" s="10"/>
       <c r="H10" s="11"/>
       <c r="I10" s="12"/>
@@ -2474,7 +2061,7 @@
       <c r="W10" s="18"/>
       <c r="X10" s="12"/>
       <c r="Y10" s="19"/>
-      <c r="AA10" s="37"/>
+      <c r="AA10" s="38"/>
       <c r="AC10" s="22"/>
       <c r="AE10" s="14"/>
       <c r="AG10" s="35"/>
@@ -2515,7 +2102,7 @@
       <c r="C11" s="8"/>
       <c r="D11" s="9"/>
       <c r="E11" s="10"/>
-      <c r="F11" s="36"/>
+      <c r="F11" s="37"/>
       <c r="G11" s="10"/>
       <c r="H11" s="11"/>
       <c r="I11" s="12"/>
@@ -2576,7 +2163,7 @@
       <c r="C12" s="8"/>
       <c r="D12" s="9"/>
       <c r="E12" s="10"/>
-      <c r="F12" s="36"/>
+      <c r="F12" s="37"/>
       <c r="G12" s="10"/>
       <c r="H12" s="11"/>
       <c r="I12" s="12"/>
@@ -2596,7 +2183,7 @@
       <c r="W12" s="18"/>
       <c r="X12" s="12"/>
       <c r="Y12" s="19"/>
-      <c r="Z12" s="38"/>
+      <c r="Z12" s="39"/>
       <c r="AA12" s="21"/>
       <c r="AC12" s="22"/>
       <c r="AE12" s="14"/>
@@ -2638,7 +2225,7 @@
       <c r="C13" s="8"/>
       <c r="D13" s="9"/>
       <c r="E13" s="10"/>
-      <c r="F13" s="36"/>
+      <c r="F13" s="37"/>
       <c r="G13" s="10"/>
       <c r="H13" s="11"/>
       <c r="I13" s="12"/>
@@ -2658,9 +2245,9 @@
       <c r="W13" s="18"/>
       <c r="X13" s="12"/>
       <c r="Y13" s="19"/>
-      <c r="Z13" s="38"/>
+      <c r="Z13" s="39"/>
       <c r="AA13" s="21"/>
-      <c r="AB13" s="38"/>
+      <c r="AB13" s="39"/>
       <c r="AC13" s="22"/>
       <c r="AE13" s="14"/>
       <c r="AG13" s="35"/>
@@ -2700,64 +2287,64 @@
       <c r="B14" s="33"/>
       <c r="C14" s="8"/>
       <c r="D14" s="9"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="36"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="37"/>
       <c r="G14" s="10"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="41"/>
-      <c r="J14" s="41"/>
-      <c r="K14" s="41"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="42"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="42"/>
       <c r="L14" s="18"/>
-      <c r="M14" s="42"/>
-      <c r="N14" s="43"/>
-      <c r="O14" s="41"/>
+      <c r="M14" s="43"/>
+      <c r="N14" s="44"/>
+      <c r="O14" s="42"/>
       <c r="P14" s="12"/>
-      <c r="Q14" s="43"/>
-      <c r="R14" s="41"/>
-      <c r="S14" s="41"/>
-      <c r="T14" s="44"/>
-      <c r="U14" s="45"/>
-      <c r="V14" s="41"/>
+      <c r="Q14" s="44"/>
+      <c r="R14" s="42"/>
+      <c r="S14" s="42"/>
+      <c r="T14" s="45"/>
+      <c r="U14" s="46"/>
+      <c r="V14" s="42"/>
       <c r="W14" s="18"/>
-      <c r="X14" s="41"/>
-      <c r="Y14" s="46"/>
+      <c r="X14" s="42"/>
+      <c r="Y14" s="47"/>
       <c r="Z14" s="35"/>
-      <c r="AA14" s="47"/>
+      <c r="AA14" s="48"/>
       <c r="AB14" s="35"/>
-      <c r="AC14" s="48"/>
+      <c r="AC14" s="49"/>
       <c r="AD14" s="35"/>
-      <c r="AE14" s="42"/>
+      <c r="AE14" s="43"/>
       <c r="AF14" s="35"/>
       <c r="AG14" s="35"/>
-      <c r="AH14" s="41"/>
+      <c r="AH14" s="42"/>
       <c r="AI14" s="25"/>
-      <c r="AJ14" s="49"/>
-      <c r="AK14" s="41"/>
-      <c r="AL14" s="44"/>
-      <c r="AM14" s="50"/>
-      <c r="AN14" s="50"/>
+      <c r="AJ14" s="50"/>
+      <c r="AK14" s="42"/>
+      <c r="AL14" s="45"/>
+      <c r="AM14" s="51"/>
+      <c r="AN14" s="51"/>
       <c r="AO14" s="14"/>
       <c r="AP14" s="15"/>
       <c r="AQ14" s="16"/>
       <c r="AR14" s="24"/>
-      <c r="AS14" s="51"/>
+      <c r="AS14" s="52"/>
       <c r="AT14" s="35"/>
       <c r="AU14" s="18"/>
-      <c r="AV14" s="52"/>
-      <c r="AW14" s="52"/>
-      <c r="AX14" s="52"/>
-      <c r="AY14" s="52"/>
-      <c r="AZ14" s="53"/>
-      <c r="BA14" s="52"/>
-      <c r="BB14" s="54"/>
-      <c r="BC14" s="54"/>
+      <c r="AV14" s="53"/>
+      <c r="AW14" s="53"/>
+      <c r="AX14" s="53"/>
+      <c r="AY14" s="53"/>
+      <c r="AZ14" s="54"/>
+      <c r="BA14" s="53"/>
+      <c r="BB14" s="55"/>
+      <c r="BC14" s="55"/>
       <c r="BD14" s="31"/>
-      <c r="BE14" s="54"/>
-      <c r="BF14" s="54"/>
+      <c r="BE14" s="55"/>
+      <c r="BF14" s="55"/>
       <c r="BG14" s="32"/>
-      <c r="BH14" s="54"/>
-      <c r="BI14" s="54"/>
-      <c r="BJ14" s="54"/>
+      <c r="BH14" s="55"/>
+      <c r="BI14" s="55"/>
+      <c r="BJ14" s="55"/>
       <c r="BK14" s="30"/>
       <c r="BL14" s="30"/>
       <c r="BM14" s="30"/>
@@ -2768,7 +2355,7 @@
       <c r="C15" s="8"/>
       <c r="D15" s="9"/>
       <c r="E15" s="10"/>
-      <c r="F15" s="36"/>
+      <c r="F15" s="37"/>
       <c r="G15" s="10"/>
       <c r="H15" s="11"/>
       <c r="I15" s="12"/>
@@ -2830,7 +2417,7 @@
       <c r="C16" s="8"/>
       <c r="D16" s="9"/>
       <c r="E16" s="10"/>
-      <c r="F16" s="36"/>
+      <c r="F16" s="37"/>
       <c r="G16" s="10"/>
       <c r="H16" s="11"/>
       <c r="I16" s="12"/>
@@ -2850,7 +2437,7 @@
       <c r="W16" s="18"/>
       <c r="X16" s="12"/>
       <c r="Y16" s="19"/>
-      <c r="Z16" s="38"/>
+      <c r="Z16" s="39"/>
       <c r="AA16" s="21"/>
       <c r="AC16" s="22"/>
       <c r="AE16" s="14"/>
@@ -2888,7 +2475,7 @@
     </row>
     <row r="17" ht="13.75" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="18" ht="13.75" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="19" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -2968,7 +2555,7 @@
       <c r="BY19" s="2"/>
       <c r="BZ19" s="2"/>
     </row>
-    <row r="20" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -3048,7 +2635,7 @@
       <c r="BY20" s="2"/>
       <c r="BZ20" s="2"/>
     </row>
-    <row r="21" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -3128,7 +2715,7 @@
       <c r="BY21" s="2"/>
       <c r="BZ21" s="2"/>
     </row>
-    <row r="22" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -3208,7 +2795,7 @@
       <c r="BY22" s="2"/>
       <c r="BZ22" s="2"/>
     </row>
-    <row r="23" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -3288,7 +2875,7 @@
       <c r="BY23" s="2"/>
       <c r="BZ23" s="2"/>
     </row>
-    <row r="24" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -3368,7 +2955,7 @@
       <c r="BY24" s="2"/>
       <c r="BZ24" s="2"/>
     </row>
-    <row r="25" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -3448,7 +3035,7 @@
       <c r="BY25" s="2"/>
       <c r="BZ25" s="2"/>
     </row>
-    <row r="26" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -3528,7 +3115,7 @@
       <c r="BY26" s="2"/>
       <c r="BZ26" s="2"/>
     </row>
-    <row r="27" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -3608,7 +3195,7 @@
       <c r="BY27" s="2"/>
       <c r="BZ27" s="2"/>
     </row>
-    <row r="28" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -3688,7 +3275,7 @@
       <c r="BY28" s="2"/>
       <c r="BZ28" s="2"/>
     </row>
-    <row r="29" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -3768,7 +3355,7 @@
       <c r="BY29" s="2"/>
       <c r="BZ29" s="2"/>
     </row>
-    <row r="30" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -3848,7 +3435,7 @@
       <c r="BY30" s="2"/>
       <c r="BZ30" s="2"/>
     </row>
-    <row r="31" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -3928,7 +3515,7 @@
       <c r="BY31" s="2"/>
       <c r="BZ31" s="2"/>
     </row>
-    <row r="32" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -4008,7 +3595,7 @@
       <c r="BY32" s="2"/>
       <c r="BZ32" s="2"/>
     </row>
-    <row r="33" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -4088,7 +3675,7 @@
       <c r="BY33" s="2"/>
       <c r="BZ33" s="2"/>
     </row>
-    <row r="34" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -4168,7 +3755,7 @@
       <c r="BY34" s="2"/>
       <c r="BZ34" s="2"/>
     </row>
-    <row r="35" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -4248,7 +3835,7 @@
       <c r="BY35" s="2"/>
       <c r="BZ35" s="2"/>
     </row>
-    <row r="36" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -4328,7 +3915,7 @@
       <c r="BY36" s="2"/>
       <c r="BZ36" s="2"/>
     </row>
-    <row r="37" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -4408,7 +3995,7 @@
       <c r="BY37" s="2"/>
       <c r="BZ37" s="2"/>
     </row>
-    <row r="38" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -4488,7 +4075,7 @@
       <c r="BY38" s="2"/>
       <c r="BZ38" s="2"/>
     </row>
-    <row r="39" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -4568,7 +4155,7 @@
       <c r="BY39" s="2"/>
       <c r="BZ39" s="2"/>
     </row>
-    <row r="40" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -4648,7 +4235,7 @@
       <c r="BY40" s="2"/>
       <c r="BZ40" s="2"/>
     </row>
-    <row r="41" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -4728,7 +4315,7 @@
       <c r="BY41" s="2"/>
       <c r="BZ41" s="2"/>
     </row>
-    <row r="42" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -4808,7 +4395,7 @@
       <c r="BY42" s="2"/>
       <c r="BZ42" s="2"/>
     </row>
-    <row r="43" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -4888,7 +4475,7 @@
       <c r="BY43" s="2"/>
       <c r="BZ43" s="2"/>
     </row>
-    <row r="44" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -4968,7 +4555,7 @@
       <c r="BY44" s="2"/>
       <c r="BZ44" s="2"/>
     </row>
-    <row r="45" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -5048,7 +4635,7 @@
       <c r="BY45" s="2"/>
       <c r="BZ45" s="2"/>
     </row>
-    <row r="46" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -5128,7 +4715,7 @@
       <c r="BY46" s="2"/>
       <c r="BZ46" s="2"/>
     </row>
-    <row r="47" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -5208,7 +4795,7 @@
       <c r="BY47" s="2"/>
       <c r="BZ47" s="2"/>
     </row>
-    <row r="48" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -5288,7 +4875,7 @@
       <c r="BY48" s="2"/>
       <c r="BZ48" s="2"/>
     </row>
-    <row r="49" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -5368,7 +4955,7 @@
       <c r="BY49" s="2"/>
       <c r="BZ49" s="2"/>
     </row>
-    <row r="50" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -5448,7 +5035,7 @@
       <c r="BY50" s="2"/>
       <c r="BZ50" s="2"/>
     </row>
-    <row r="51" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="51" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -5528,7 +5115,7 @@
       <c r="BY51" s="2"/>
       <c r="BZ51" s="2"/>
     </row>
-    <row r="52" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -5608,7 +5195,7 @@
       <c r="BY52" s="2"/>
       <c r="BZ52" s="2"/>
     </row>
-    <row r="53" ht="14.5" customHeight="1" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>

--- a/Data/Hires/Workday_NewHire_Spain_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Spain_Regression_PK17.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FD5846E-B481-4AE8-BD73-6DB59E2717CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57CAB1BC-F320-49A1-A0DD-6C8BF9816CA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="121">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -222,7 +222,7 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t>10698852</t>
+    <t>10698999</t>
   </si>
   <si>
     <t>Passed</t>
@@ -231,12 +231,6 @@
     <t>356 Recruitment (Posob Zujefy Pyronu (2577) (Inherited))</t>
   </si>
   <si>
-    <t>SpainNmg</t>
-  </si>
-  <si>
-    <t>DryrunPK17</t>
-  </si>
-  <si>
     <t>SLName</t>
   </si>
   <si>
@@ -333,7 +327,7 @@
     <t>ID Card (DNI) Number</t>
   </si>
   <si>
-    <t>10006461A</t>
+    <t>10006465A</t>
   </si>
   <si>
     <t>BBVAESMM111</t>
@@ -354,16 +348,13 @@
     <t>Test_2</t>
   </si>
   <si>
-    <t>10698853</t>
+    <t>10699000</t>
   </si>
   <si>
     <t>365 Store Management (Cisuw Hapagu Pahame (10274587))</t>
   </si>
   <si>
-    <t>SpainMg</t>
-  </si>
-  <si>
-    <t>Auto 6988751</t>
+    <t>Auto 87795665</t>
   </si>
   <si>
     <t>Permanent</t>
@@ -388,10 +379,22 @@
 </t>
   </si>
   <si>
-    <t>10006462A</t>
+    <t>10006466A</t>
   </si>
   <si>
     <t>54 - ENSEÑANZAS UNIVERSITARIAS DE PRIMER CICLO Y EQUIVALENTES</t>
+  </si>
+  <si>
+    <t>Tyree</t>
+  </si>
+  <si>
+    <t>Davis</t>
+  </si>
+  <si>
+    <t>Waldo</t>
+  </si>
+  <si>
+    <t>Schinner</t>
   </si>
 </sst>
 </file>
@@ -1301,280 +1304,280 @@
         <v>65</v>
       </c>
       <c r="E2" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="G2" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="H2" s="11" t="s">
         <v>67</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>69</v>
       </c>
       <c r="I2" s="12">
         <v>919193394</v>
       </c>
       <c r="J2" s="12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K2" s="12" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="L2" s="13">
         <f t="shared" ref="L2:L3" ca="1" si="0">TODAY()-7</f>
-        <v>45772</v>
+        <v>45779</v>
       </c>
       <c r="M2" s="14" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N2" s="15" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="O2" s="12">
         <v>44</v>
       </c>
       <c r="P2" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q2" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="R2" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="S2" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="T2" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="Q2" s="15" t="s">
+      <c r="U2" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="R2" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="S2" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="T2" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="U2" s="17" t="s">
-        <v>76</v>
-      </c>
       <c r="V2" s="12" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="W2" s="18">
         <f t="shared" ref="W2:W3" ca="1" si="1">TODAY()-7</f>
-        <v>45772</v>
+        <v>45779</v>
       </c>
       <c r="X2" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="Y2" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z2" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="Y2" s="19" t="s">
+      <c r="AA2" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="Z2" s="20" t="s">
+      <c r="AB2" t="s">
         <v>79</v>
-      </c>
-      <c r="AA2" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>81</v>
       </c>
       <c r="AC2" s="22">
         <v>356</v>
       </c>
       <c r="AD2" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="AE2" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="AF2" t="s">
         <v>82</v>
-      </c>
-      <c r="AE2" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>84</v>
       </c>
       <c r="AG2" s="24">
         <f ca="1">TODAY()+365</f>
-        <v>46144</v>
+        <v>46151</v>
       </c>
       <c r="AH2" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="AI2" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="AJ2" t="s">
         <v>85</v>
       </c>
-      <c r="AI2" s="25" t="s">
+      <c r="AK2" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AL2" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="AK2" s="12" t="s">
+      <c r="AM2" s="26" t="s">
         <v>88</v>
-      </c>
-      <c r="AL2" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="AM2" s="26" t="s">
-        <v>90</v>
       </c>
       <c r="AN2" s="26">
         <f t="shared" ref="AN2:AN3" ca="1" si="2">TODAY()+7</f>
-        <v>45786</v>
+        <v>45793</v>
       </c>
       <c r="AO2" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="AP2" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="AQ2" s="16" t="s">
         <v>91</v>
-      </c>
-      <c r="AP2" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="AQ2" s="16" t="s">
-        <v>93</v>
       </c>
       <c r="AR2" s="24">
         <f t="shared" ref="AR2:AR3" ca="1" si="3">TODAY()+365</f>
-        <v>46144</v>
+        <v>46151</v>
       </c>
       <c r="AS2" s="27" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="AT2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="AU2" s="13">
         <v>29221</v>
       </c>
       <c r="AV2" s="28" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="AW2" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="AX2" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY2" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="AZ2" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="AX2" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="AY2" s="28" t="s">
+      <c r="BA2" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="BB2" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="BC2" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="AZ2" s="29" t="s">
+      <c r="BD2" s="31">
+        <v>281000757380</v>
+      </c>
+      <c r="BE2" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="BF2" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="BA2" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="BB2" s="30" t="s">
-        <v>69</v>
-      </c>
-      <c r="BC2" s="30" t="s">
+      <c r="BG2" s="32" t="s">
         <v>98</v>
       </c>
-      <c r="BD2" s="31">
-        <v>281000756976</v>
-      </c>
-      <c r="BE2" s="30" t="s">
-        <v>69</v>
-      </c>
-      <c r="BF2" s="30" t="s">
+      <c r="BH2" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="BG2" s="32" t="s">
+      <c r="BI2" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="BH2" s="30" t="s">
+      <c r="BJ2" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="BI2" s="30" t="s">
+      <c r="BK2" s="30" t="s">
         <v>102</v>
-      </c>
-      <c r="BJ2" s="30" t="s">
-        <v>103</v>
-      </c>
-      <c r="BK2" s="30" t="s">
-        <v>104</v>
       </c>
       <c r="BL2" s="30">
         <v>36526</v>
       </c>
       <c r="BM2" s="30" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="33" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B3" s="34" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>64</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="F3" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="H3" s="11" t="s">
         <v>67</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>69</v>
       </c>
       <c r="I3" s="12">
         <v>919193436</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="K3" s="12" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="L3" s="13">
         <f t="shared" ca="1" si="0"/>
-        <v>45772</v>
+        <v>45779</v>
       </c>
       <c r="M3" s="14" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="O3" s="12">
         <v>44</v>
       </c>
       <c r="P3" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="Q3" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="R3" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="S3" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="T3" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="Q3" s="15" t="s">
+      <c r="U3" s="15" t="s">
         <v>74</v>
       </c>
-      <c r="R3" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="S3" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="T3" s="16" t="s">
-        <v>75</v>
-      </c>
-      <c r="U3" s="15" t="s">
-        <v>76</v>
-      </c>
       <c r="V3" s="12" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="W3" s="18">
         <f t="shared" ca="1" si="1"/>
-        <v>45772</v>
+        <v>45779</v>
       </c>
       <c r="X3" s="12" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="Y3" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>108</v>
+      </c>
+      <c r="AA3" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="AB3" t="s">
         <v>110</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>111</v>
-      </c>
-      <c r="AA3" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>113</v>
       </c>
       <c r="AC3" s="22">
         <v>365</v>
@@ -1583,111 +1586,111 @@
         <v>100</v>
       </c>
       <c r="AE3" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>111</v>
+      </c>
+      <c r="AG3" s="35" t="s">
+        <v>76</v>
+      </c>
+      <c r="AH3" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="AF3" t="s">
+      <c r="AI3" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AK3" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL3" s="16" t="s">
         <v>114</v>
       </c>
-      <c r="AG3" s="35" t="s">
-        <v>78</v>
-      </c>
-      <c r="AH3" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="AI3" s="25" t="s">
-        <v>115</v>
-      </c>
-      <c r="AJ3" t="s">
-        <v>116</v>
-      </c>
-      <c r="AK3" s="12" t="s">
+      <c r="AM3" s="26" t="s">
         <v>88</v>
-      </c>
-      <c r="AL3" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="AM3" s="26" t="s">
-        <v>90</v>
       </c>
       <c r="AN3" s="26">
         <f t="shared" ca="1" si="2"/>
-        <v>45786</v>
+        <v>45793</v>
       </c>
       <c r="AO3" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="AP3" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="AQ3" s="16" t="s">
         <v>91</v>
-      </c>
-      <c r="AP3" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="AQ3" s="16" t="s">
-        <v>93</v>
       </c>
       <c r="AR3" s="24">
         <f t="shared" ca="1" si="3"/>
-        <v>46144</v>
+        <v>46151</v>
       </c>
       <c r="AS3" s="27" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="AT3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="AU3" s="13">
         <v>29221</v>
       </c>
       <c r="AV3" s="28" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="AW3" s="28" t="s">
+        <v>93</v>
+      </c>
+      <c r="AX3" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY3" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="AZ3" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="AX3" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="AY3" s="28" t="s">
+      <c r="BA3" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="BB3" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="BC3" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="AZ3" s="29" t="s">
+      <c r="BD3" s="31">
+        <v>281000757481</v>
+      </c>
+      <c r="BE3" s="30" t="s">
+        <v>67</v>
+      </c>
+      <c r="BF3" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="BA3" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="BB3" s="30" t="s">
-        <v>69</v>
-      </c>
-      <c r="BC3" s="30" t="s">
-        <v>98</v>
-      </c>
-      <c r="BD3" s="31">
-        <v>281000757077</v>
-      </c>
-      <c r="BE3" s="30" t="s">
-        <v>69</v>
-      </c>
-      <c r="BF3" s="30" t="s">
+      <c r="BG3" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="BH3" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="BG3" s="32" t="s">
-        <v>118</v>
-      </c>
-      <c r="BH3" s="30" t="s">
+      <c r="BI3" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="BJ3" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="BI3" s="30" t="s">
-        <v>102</v>
-      </c>
-      <c r="BJ3" s="30" t="s">
-        <v>103</v>
-      </c>
       <c r="BK3" s="30" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="BL3" s="30">
         <v>36526</v>
       </c>
       <c r="BM3" s="30" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
@@ -5392,6 +5395,6 @@
     <hyperlink ref="U2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId2"/>
 </worksheet>
 </file>
--- a/Data/Hires/Workday_NewHire_Spain_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Spain_Regression_PK17.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="122">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -208,7 +208,7 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t>10699543</t>
+    <t>10699624</t>
   </si>
   <si>
     <t>Passed</t>
@@ -217,7 +217,7 @@
     <t>356 Recruitment (Posob Zujefy Pyronu (2577) (Inherited))</t>
   </si>
   <si>
-    <t>Mrs</t>
+    <t>NineJune</t>
   </si>
   <si>
     <t>GSKSKk</t>
@@ -319,7 +319,7 @@
     <t>ID Card (DNI) Number</t>
   </si>
   <si>
-    <t>10006501A</t>
+    <t>10006512A</t>
   </si>
   <si>
     <t>BBVAESMM111</t>
@@ -340,19 +340,22 @@
     <t>Test_2</t>
   </si>
   <si>
-    <t>10699544</t>
+    <t>10699625</t>
   </si>
   <si>
     <t>365 Store Management (Cisuw Hapagu Pahame (10274587))</t>
   </si>
   <si>
+    <t>NineJuneTwetyFive</t>
+  </si>
+  <si>
     <t>SchirRR</t>
   </si>
   <si>
     <t>SLNameTwoo</t>
   </si>
   <si>
-    <t>Auto 28086090</t>
+    <t>Auto 24471201</t>
   </si>
   <si>
     <t>Permanent</t>
@@ -377,7 +380,7 @@
 </t>
   </si>
   <si>
-    <t>10006502A</t>
+    <t>10006513A</t>
   </si>
   <si>
     <t>54 - ENSEÑANZAS UNIVERSITARIAS DE PRIMER CICLO Y EQUIVALENTES</t>
@@ -1303,7 +1306,7 @@
       </c>
       <c r="L2" s="13">
         <f t="shared" ref="L2" si="0">TODAY()-7</f>
-        <v>45803</v>
+        <v>45810</v>
       </c>
       <c r="M2" s="14" t="s">
         <v>69</v>
@@ -1337,7 +1340,7 @@
       </c>
       <c r="W2" s="18">
         <f t="shared" ref="W2" si="1">TODAY()-7</f>
-        <v>45803</v>
+        <v>45810</v>
       </c>
       <c r="X2" s="12" t="s">
         <v>77</v>
@@ -1368,7 +1371,7 @@
       </c>
       <c r="AG2" s="24">
         <f>TODAY()+365</f>
-        <v>46175</v>
+        <v>46182</v>
       </c>
       <c r="AH2" s="12" t="s">
         <v>85</v>
@@ -1390,7 +1393,7 @@
       </c>
       <c r="AN2" s="26">
         <f t="shared" ref="AN2" si="2">TODAY()+7</f>
-        <v>45817</v>
+        <v>45824</v>
       </c>
       <c r="AO2" s="14" t="s">
         <v>91</v>
@@ -1403,7 +1406,7 @@
       </c>
       <c r="AR2" s="24">
         <f t="shared" ref="AR2" si="3">TODAY()+365</f>
-        <v>46175</v>
+        <v>46182</v>
       </c>
       <c r="AS2" s="27" t="s">
         <v>91</v>
@@ -1439,7 +1442,7 @@
         <v>98</v>
       </c>
       <c r="BD2" s="31">
-        <v>281000757497</v>
+        <v>281000757500</v>
       </c>
       <c r="BE2" s="30" t="s">
         <v>69</v>
@@ -1483,13 +1486,13 @@
         <v>108</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>66</v>
+        <v>109</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H3" s="11" t="s">
         <v>69</v>
@@ -1543,16 +1546,16 @@
         <v>77</v>
       </c>
       <c r="Y3" s="19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Z3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AA3" s="21" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AB3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AC3" s="22">
         <v>365</v>
@@ -1564,7 +1567,7 @@
         <v>83</v>
       </c>
       <c r="AF3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG3" s="35" t="s">
         <v>78</v>
@@ -1573,16 +1576,16 @@
         <v>85</v>
       </c>
       <c r="AI3" s="25" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AJ3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AK3" s="12" t="s">
         <v>88</v>
       </c>
       <c r="AL3" s="36" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AM3" s="26" t="s">
         <v>90</v>
@@ -1636,7 +1639,7 @@
         <v>98</v>
       </c>
       <c r="BD3" s="31">
-        <v>281000757498</v>
+        <v>281000757501</v>
       </c>
       <c r="BE3" s="30" t="s">
         <v>69</v>
@@ -1645,7 +1648,7 @@
         <v>99</v>
       </c>
       <c r="BG3" s="32" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="BH3" s="30" t="s">
         <v>101</v>
@@ -1657,7 +1660,7 @@
         <v>103</v>
       </c>
       <c r="BK3" s="30" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="BL3" s="30">
         <v>36526</v>

--- a/Data/Hires/Workday_NewHire_Spain_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Spain_Regression_PK17.xlsx
@@ -1,37 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57CAB1BC-F320-49A1-A0DD-6C8BF9816CA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="1068" yWindow="-108" windowWidth="22080" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="Sheet1" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase">Sheet1!$A$1:$BY$53</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="121">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -222,7 +208,7 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t>10698999</t>
+    <t>10699765</t>
   </si>
   <si>
     <t>Passed</t>
@@ -231,7 +217,13 @@
     <t>356 Recruitment (Posob Zujefy Pyronu (2577) (Inherited))</t>
   </si>
   <si>
-    <t>SLName</t>
+    <t>TwentyJune</t>
+  </si>
+  <si>
+    <t>GSK</t>
+  </si>
+  <si>
+    <t>NewOne</t>
   </si>
   <si>
     <t>Spain</t>
@@ -327,7 +319,7 @@
     <t>ID Card (DNI) Number</t>
   </si>
   <si>
-    <t>10006465A</t>
+    <t>10006525A</t>
   </si>
   <si>
     <t>BBVAESMM111</t>
@@ -348,13 +340,19 @@
     <t>Test_2</t>
   </si>
   <si>
-    <t>10699000</t>
-  </si>
-  <si>
     <t>365 Store Management (Cisuw Hapagu Pahame (10274587))</t>
   </si>
   <si>
-    <t>Auto 87795665</t>
+    <t>EighteenJune</t>
+  </si>
+  <si>
+    <t>SchirRR</t>
+  </si>
+  <si>
+    <t>SLNameTwoo</t>
+  </si>
+  <si>
+    <t>Auto 8092876</t>
   </si>
   <si>
     <t>Permanent</t>
@@ -379,122 +377,110 @@
 </t>
   </si>
   <si>
-    <t>10006466A</t>
+    <t>10006514A</t>
   </si>
   <si>
     <t>54 - ENSEÑANZAS UNIVERSITARIAS DE PRIMER CICLO Y EQUIVALENTES</t>
-  </si>
-  <si>
-    <t>Tyree</t>
-  </si>
-  <si>
-    <t>Davis</t>
-  </si>
-  <si>
-    <t>Waldo</t>
-  </si>
-  <si>
-    <t>Schinner</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
   </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
+      <sz val="10"/>
+      <name val="Calibri Light"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri Light"/>
       <family val="2"/>
       <scheme val="major"/>
+      <sz val="10"/>
+      <name val="Calibri Light"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <color theme="1"/>
+      <family val="2"/>
       <sz val="14"/>
-      <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
-      <sz val="10"/>
       <color indexed="8"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="10"/>
+      <name val="Calibri"/>
     </font>
     <font>
+      <color theme="1"/>
+      <family val="2"/>
       <sz val="11"/>
-      <color theme="1"/>
       <name val="Segoe UI"/>
-      <family val="2"/>
     </font>
     <font>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <color rgb="FFFF0000"/>
+      <family val="2"/>
       <sz val="14"/>
-      <color rgb="FFFF0000"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="8">
@@ -528,13 +514,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor theme="5" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
+        <fgColor theme="4" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -548,18 +534,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -569,19 +547,15 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -596,7 +570,7 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -677,6 +651,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1011,89 +988,89 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BZ54"/>
-  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" customWidth="1"/>
-    <col min="2" max="2" width="11.109375" customWidth="1"/>
-    <col min="3" max="3" width="10.21875" customWidth="1"/>
-    <col min="4" max="4" width="41.44140625" customWidth="1"/>
+    <col min="1" max="1" width="11.36328125" customWidth="1"/>
+    <col min="2" max="2" width="51.36328125" customWidth="1"/>
+    <col min="3" max="3" width="10.1796875" customWidth="1"/>
+    <col min="4" max="4" width="41.453125" customWidth="1"/>
     <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="13.44140625" customWidth="1"/>
-    <col min="7" max="7" width="21.77734375" customWidth="1"/>
-    <col min="8" max="8" width="13.44140625" customWidth="1"/>
+    <col min="6" max="6" width="13.453125" customWidth="1"/>
+    <col min="7" max="7" width="21.81640625" customWidth="1"/>
+    <col min="8" max="8" width="13.453125" customWidth="1"/>
     <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="5.6640625" customWidth="1"/>
-    <col min="11" max="11" width="12.44140625" customWidth="1"/>
-    <col min="12" max="12" width="12.21875" customWidth="1"/>
-    <col min="13" max="13" width="20.6640625" customWidth="1"/>
-    <col min="14" max="14" width="12.6640625" customWidth="1"/>
-    <col min="15" max="15" width="10.77734375" customWidth="1"/>
-    <col min="16" max="16" width="8.109375" customWidth="1"/>
-    <col min="17" max="17" width="13.21875" customWidth="1"/>
-    <col min="18" max="18" width="11.88671875" customWidth="1"/>
-    <col min="19" max="19" width="8.109375" customWidth="1"/>
-    <col min="20" max="20" width="5.6640625" customWidth="1"/>
-    <col min="21" max="21" width="12.33203125" customWidth="1"/>
+    <col min="10" max="10" width="5.6328125" customWidth="1"/>
+    <col min="11" max="11" width="12.453125" customWidth="1"/>
+    <col min="12" max="12" width="12.1796875" customWidth="1"/>
+    <col min="13" max="13" width="20.6328125" customWidth="1"/>
+    <col min="14" max="14" width="12.6328125" customWidth="1"/>
+    <col min="15" max="15" width="10.81640625" customWidth="1"/>
+    <col min="16" max="16" width="8.08984375" customWidth="1"/>
+    <col min="17" max="17" width="13.1796875" customWidth="1"/>
+    <col min="18" max="18" width="11.90625" customWidth="1"/>
+    <col min="19" max="19" width="8.08984375" customWidth="1"/>
+    <col min="20" max="20" width="5.6328125" customWidth="1"/>
+    <col min="21" max="21" width="12.36328125" customWidth="1"/>
     <col min="22" max="22" width="17" customWidth="1"/>
-    <col min="23" max="24" width="10.5546875" customWidth="1"/>
-    <col min="25" max="25" width="8.109375" customWidth="1"/>
-    <col min="26" max="26" width="23.109375" customWidth="1"/>
-    <col min="27" max="27" width="19.6640625" style="1" customWidth="1"/>
-    <col min="28" max="28" width="9.21875" customWidth="1"/>
-    <col min="29" max="29" width="9.21875" style="1" customWidth="1"/>
-    <col min="30" max="30" width="8.44140625" customWidth="1"/>
-    <col min="31" max="31" width="12.109375" customWidth="1"/>
-    <col min="32" max="32" width="9.44140625" customWidth="1"/>
-    <col min="33" max="33" width="11.21875" customWidth="1"/>
-    <col min="34" max="34" width="22.88671875" customWidth="1"/>
-    <col min="35" max="35" width="15.21875" customWidth="1"/>
-    <col min="36" max="36" width="14.109375" customWidth="1"/>
+    <col min="23" max="24" width="10.54296875" customWidth="1"/>
+    <col min="25" max="25" width="8.08984375" customWidth="1"/>
+    <col min="26" max="26" width="23.08984375" customWidth="1"/>
+    <col min="27" max="27" width="19.6328125" style="1" customWidth="1"/>
+    <col min="28" max="28" width="9.1796875" customWidth="1"/>
+    <col min="29" max="29" width="9.1796875" style="1" customWidth="1"/>
+    <col min="30" max="30" width="8.453125" customWidth="1"/>
+    <col min="31" max="31" width="12.08984375" customWidth="1"/>
+    <col min="32" max="32" width="9.453125" customWidth="1"/>
+    <col min="33" max="33" width="11.1796875" customWidth="1"/>
+    <col min="34" max="34" width="22.90625" customWidth="1"/>
+    <col min="35" max="35" width="15.1796875" customWidth="1"/>
+    <col min="36" max="36" width="14.08984375" customWidth="1"/>
     <col min="37" max="37" width="26" customWidth="1"/>
-    <col min="38" max="38" width="13.109375" style="1" customWidth="1"/>
-    <col min="39" max="39" width="19.21875" customWidth="1"/>
-    <col min="40" max="40" width="16.88671875" customWidth="1"/>
-    <col min="41" max="41" width="25.21875" customWidth="1"/>
-    <col min="42" max="42" width="12.6640625" customWidth="1"/>
-    <col min="43" max="43" width="6.5546875" customWidth="1"/>
-    <col min="44" max="44" width="19.33203125" customWidth="1"/>
-    <col min="45" max="45" width="19.109375" customWidth="1"/>
-    <col min="46" max="46" width="15.88671875" customWidth="1"/>
-    <col min="47" max="47" width="19.21875" customWidth="1"/>
-    <col min="48" max="48" width="23.44140625" customWidth="1"/>
-    <col min="49" max="49" width="14.6640625" customWidth="1"/>
-    <col min="50" max="50" width="23.109375" customWidth="1"/>
-    <col min="51" max="51" width="28.6640625" customWidth="1"/>
-    <col min="52" max="52" width="17.77734375" customWidth="1"/>
-    <col min="53" max="53" width="22.44140625" customWidth="1"/>
-    <col min="54" max="54" width="17.77734375" customWidth="1"/>
+    <col min="38" max="38" width="13.08984375" style="1" customWidth="1"/>
+    <col min="39" max="39" width="19.1796875" customWidth="1"/>
+    <col min="40" max="40" width="16.90625" customWidth="1"/>
+    <col min="41" max="41" width="25.1796875" customWidth="1"/>
+    <col min="42" max="42" width="12.6328125" customWidth="1"/>
+    <col min="43" max="43" width="6.54296875" customWidth="1"/>
+    <col min="44" max="44" width="19.36328125" customWidth="1"/>
+    <col min="45" max="45" width="19.08984375" customWidth="1"/>
+    <col min="46" max="46" width="15.90625" customWidth="1"/>
+    <col min="47" max="47" width="19.1796875" customWidth="1"/>
+    <col min="48" max="48" width="23.453125" customWidth="1"/>
+    <col min="49" max="49" width="14.6328125" customWidth="1"/>
+    <col min="50" max="50" width="23.08984375" customWidth="1"/>
+    <col min="51" max="51" width="28.6328125" customWidth="1"/>
+    <col min="52" max="52" width="17.81640625" customWidth="1"/>
+    <col min="53" max="53" width="22.453125" customWidth="1"/>
+    <col min="54" max="54" width="17.81640625" customWidth="1"/>
     <col min="55" max="55" width="18" customWidth="1"/>
-    <col min="56" max="56" width="13.109375" customWidth="1"/>
-    <col min="57" max="57" width="15.5546875" customWidth="1"/>
-    <col min="58" max="58" width="18.88671875" customWidth="1"/>
-    <col min="59" max="59" width="10.77734375" customWidth="1"/>
-    <col min="60" max="60" width="27.33203125" customWidth="1"/>
+    <col min="56" max="56" width="13.08984375" customWidth="1"/>
+    <col min="57" max="57" width="15.54296875" customWidth="1"/>
+    <col min="58" max="58" width="18.90625" customWidth="1"/>
+    <col min="59" max="59" width="10.81640625" customWidth="1"/>
+    <col min="60" max="60" width="27.36328125" customWidth="1"/>
     <col min="61" max="61" width="12" customWidth="1"/>
-    <col min="62" max="62" width="9.109375" customWidth="1"/>
-    <col min="63" max="63" width="15.5546875" customWidth="1"/>
-    <col min="64" max="64" width="10.77734375" customWidth="1"/>
-    <col min="65" max="65" width="9.77734375" customWidth="1"/>
-    <col min="66" max="66" width="11.33203125" customWidth="1"/>
-    <col min="67" max="67" width="14.21875" customWidth="1"/>
+    <col min="62" max="62" width="9.08984375" customWidth="1"/>
+    <col min="63" max="63" width="15.54296875" customWidth="1"/>
+    <col min="64" max="64" width="10.81640625" customWidth="1"/>
+    <col min="65" max="65" width="9.81640625" customWidth="1"/>
+    <col min="66" max="66" width="11.36328125" customWidth="1"/>
+    <col min="67" max="67" width="14.1796875" customWidth="1"/>
     <col min="68" max="68" width="17" customWidth="1"/>
-    <col min="69" max="69" width="16.33203125" customWidth="1"/>
-    <col min="70" max="70" width="12.5546875" customWidth="1"/>
-    <col min="71" max="71" width="21.6640625" customWidth="1"/>
-    <col min="72" max="72" width="12.21875" customWidth="1"/>
-    <col min="73" max="73" width="27.44140625" customWidth="1"/>
-    <col min="74" max="74" width="29.21875" customWidth="1"/>
-    <col min="75" max="75" width="8.44140625" customWidth="1"/>
-    <col min="76" max="76" width="26.88671875" customWidth="1"/>
-    <col min="77" max="77" width="22.33203125" customWidth="1"/>
+    <col min="69" max="69" width="16.36328125" customWidth="1"/>
+    <col min="70" max="70" width="12.54296875" customWidth="1"/>
+    <col min="71" max="71" width="21.6328125" customWidth="1"/>
+    <col min="72" max="72" width="12.1796875" customWidth="1"/>
+    <col min="73" max="73" width="27.453125" customWidth="1"/>
+    <col min="74" max="74" width="29.1796875" customWidth="1"/>
+    <col min="75" max="75" width="8.453125" customWidth="1"/>
+    <col min="76" max="76" width="26.90625" customWidth="1"/>
+    <col min="77" max="77" width="22.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="14.5" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1290,7 +1267,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>62</v>
       </c>
@@ -1304,280 +1281,278 @@
         <v>65</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>117</v>
+        <v>66</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>118</v>
+        <v>67</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I2" s="12">
         <v>919193394</v>
       </c>
       <c r="J2" s="12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K2" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="L2" s="13">
+        <f t="shared" ref="L2" si="0">TODAY()-7</f>
+        <v>45820</v>
+      </c>
+      <c r="M2" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="L2" s="13">
-        <f t="shared" ref="L2:L3" ca="1" si="0">TODAY()-7</f>
-        <v>45779</v>
-      </c>
-      <c r="M2" s="14" t="s">
-        <v>67</v>
-      </c>
       <c r="N2" s="15" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="O2" s="12">
         <v>44</v>
       </c>
       <c r="P2" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q2" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="R2" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="S2" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="Q2" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="R2" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="S2" s="12" t="s">
-        <v>69</v>
-      </c>
       <c r="T2" s="16" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="U2" s="17" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="V2" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="W2" s="18">
-        <f t="shared" ref="W2:W3" ca="1" si="1">TODAY()-7</f>
-        <v>45779</v>
+        <f t="shared" ref="W2" si="1">TODAY()-7</f>
+        <v>45820</v>
       </c>
       <c r="X2" s="12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="Y2" s="19" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="Z2" s="20" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AA2" s="21" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="AB2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="AC2" s="22">
         <v>356</v>
       </c>
       <c r="AD2" s="23" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AE2" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AF2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="AG2" s="24">
-        <f ca="1">TODAY()+365</f>
-        <v>46151</v>
+        <f>TODAY()+365</f>
+        <v>46192</v>
       </c>
       <c r="AH2" s="12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AI2" s="25" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="AJ2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AK2" s="12" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AL2" s="16" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="AM2" s="26" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AN2" s="26">
-        <f t="shared" ref="AN2:AN3" ca="1" si="2">TODAY()+7</f>
-        <v>45793</v>
+        <f t="shared" ref="AN2" si="2">TODAY()+7</f>
+        <v>45834</v>
       </c>
       <c r="AO2" s="14" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AP2" s="15" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AQ2" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="AR2" s="24">
+        <f t="shared" ref="AR2" si="3">TODAY()+365</f>
+        <v>46192</v>
+      </c>
+      <c r="AS2" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="AR2" s="24">
-        <f t="shared" ref="AR2:AR3" ca="1" si="3">TODAY()+365</f>
-        <v>46151</v>
-      </c>
-      <c r="AS2" s="27" t="s">
-        <v>89</v>
-      </c>
       <c r="AT2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AU2" s="13">
         <v>29221</v>
       </c>
       <c r="AV2" s="28" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AW2" s="28" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AX2" s="28" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AY2" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="AZ2" s="29" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="BA2" s="28" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="BB2" s="30" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="BC2" s="30" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BD2" s="31">
-        <v>281000757380</v>
+        <v>281000757510</v>
       </c>
       <c r="BE2" s="30" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="BF2" s="30" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="BG2" s="32" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="BH2" s="30" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="BI2" s="30" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="BJ2" s="30" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="BK2" s="30" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="BL2" s="30">
         <v>36526</v>
       </c>
       <c r="BM2" s="30" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
-    <row r="3" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="33" t="s">
-        <v>104</v>
-      </c>
-      <c r="B3" s="34" t="s">
-        <v>105</v>
+        <v>106</v>
+      </c>
+      <c r="B3" s="34">
+        <v>10699752</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>64</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="F3" s="10" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>66</v>
+        <v>110</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I3" s="12">
         <v>919193436</v>
       </c>
       <c r="J3" s="12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K3" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="L3" s="13">
+        <v>45800</v>
+      </c>
+      <c r="M3" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="L3" s="13">
-        <f t="shared" ca="1" si="0"/>
-        <v>45779</v>
-      </c>
-      <c r="M3" s="14" t="s">
-        <v>67</v>
-      </c>
       <c r="N3" s="15" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="O3" s="12">
         <v>44</v>
       </c>
-      <c r="P3" s="12" t="s">
+      <c r="P3" s="12">
+        <v>28013</v>
+      </c>
+      <c r="Q3" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="R3" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="S3" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="Q3" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="R3" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="S3" s="12" t="s">
-        <v>69</v>
-      </c>
       <c r="T3" s="16" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="U3" s="15" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="V3" s="12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="W3" s="18">
-        <f t="shared" ca="1" si="1"/>
-        <v>45779</v>
+        <v>45800</v>
       </c>
       <c r="X3" s="12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="Y3" s="19" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="Z3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="AA3" s="21" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="AB3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="AC3" s="22">
         <v>365</v>
@@ -1586,120 +1561,118 @@
         <v>100</v>
       </c>
       <c r="AE3" s="14" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="AF3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="AG3" s="35" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="AH3" s="12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="AI3" s="25" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="AJ3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AK3" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="AL3" s="16" t="s">
-        <v>114</v>
+        <v>88</v>
+      </c>
+      <c r="AL3" s="36" t="s">
+        <v>118</v>
       </c>
       <c r="AM3" s="26" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AN3" s="26">
-        <f t="shared" ca="1" si="2"/>
-        <v>45793</v>
+        <v>45814</v>
       </c>
       <c r="AO3" s="14" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AP3" s="15" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="AQ3" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="AR3" s="24">
+        <v>46172</v>
+      </c>
+      <c r="AS3" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="AR3" s="24">
-        <f t="shared" ca="1" si="3"/>
-        <v>46151</v>
-      </c>
-      <c r="AS3" s="27" t="s">
-        <v>89</v>
-      </c>
       <c r="AT3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="AU3" s="13">
         <v>29221</v>
       </c>
       <c r="AV3" s="28" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="AW3" s="28" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="AX3" s="28" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="AY3" s="28" t="s">
-        <v>94</v>
-      </c>
-      <c r="AZ3" s="29" t="s">
-        <v>95</v>
+        <v>96</v>
+      </c>
+      <c r="AZ3" s="29">
+        <v>40844</v>
       </c>
       <c r="BA3" s="28" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="BB3" s="30" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="BC3" s="30" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="BD3" s="31">
-        <v>281000757481</v>
+        <v>281000757503</v>
       </c>
       <c r="BE3" s="30" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="BF3" s="30" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="BG3" s="32" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="BH3" s="30" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="BI3" s="30" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="BJ3" s="30" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="BK3" s="30" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="BL3" s="30">
         <v>36526</v>
       </c>
       <c r="BM3" s="30" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
-    <row r="4" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="33"/>
       <c r="B4" s="6"/>
       <c r="C4" s="8"/>
       <c r="D4" s="9"/>
       <c r="E4" s="10"/>
-      <c r="F4" s="36"/>
+      <c r="F4" s="37"/>
       <c r="G4" s="10"/>
       <c r="H4" s="11"/>
       <c r="I4" s="12"/>
@@ -1754,13 +1727,13 @@
       <c r="BL4" s="30"/>
       <c r="BM4" s="30"/>
     </row>
-    <row r="5" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="33"/>
       <c r="B5" s="33"/>
       <c r="C5" s="8"/>
       <c r="D5" s="9"/>
       <c r="E5" s="10"/>
-      <c r="F5" s="36"/>
+      <c r="F5" s="37"/>
       <c r="G5" s="10"/>
       <c r="H5" s="11"/>
       <c r="I5" s="12"/>
@@ -1816,13 +1789,13 @@
       <c r="BL5" s="30"/>
       <c r="BM5" s="30"/>
     </row>
-    <row r="6" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="33"/>
       <c r="B6" s="33"/>
       <c r="C6" s="8"/>
       <c r="D6" s="9"/>
       <c r="E6" s="10"/>
-      <c r="F6" s="36"/>
+      <c r="F6" s="37"/>
       <c r="G6" s="10"/>
       <c r="H6" s="11"/>
       <c r="I6" s="12"/>
@@ -1878,13 +1851,13 @@
       <c r="BL6" s="30"/>
       <c r="BM6" s="30"/>
     </row>
-    <row r="7" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="33"/>
       <c r="B7" s="33"/>
       <c r="C7" s="8"/>
       <c r="D7" s="9"/>
       <c r="E7" s="10"/>
-      <c r="F7" s="36"/>
+      <c r="F7" s="37"/>
       <c r="G7" s="10"/>
       <c r="H7" s="11"/>
       <c r="I7" s="12"/>
@@ -1939,13 +1912,13 @@
       <c r="BL7" s="30"/>
       <c r="BM7" s="30"/>
     </row>
-    <row r="8" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="33"/>
       <c r="B8" s="33"/>
       <c r="C8" s="8"/>
       <c r="D8" s="9"/>
       <c r="E8" s="10"/>
-      <c r="F8" s="36"/>
+      <c r="F8" s="37"/>
       <c r="G8" s="10"/>
       <c r="H8" s="11"/>
       <c r="I8" s="12"/>
@@ -2000,13 +1973,13 @@
       <c r="BL8" s="30"/>
       <c r="BM8" s="30"/>
     </row>
-    <row r="9" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="33"/>
       <c r="B9" s="33"/>
       <c r="C9" s="8"/>
       <c r="D9" s="9"/>
       <c r="E9" s="10"/>
-      <c r="F9" s="36"/>
+      <c r="F9" s="37"/>
       <c r="G9" s="10"/>
       <c r="H9" s="11"/>
       <c r="I9" s="12"/>
@@ -2062,13 +2035,13 @@
       <c r="BL9" s="30"/>
       <c r="BM9" s="30"/>
     </row>
-    <row r="10" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="33"/>
       <c r="B10" s="33"/>
       <c r="C10" s="8"/>
       <c r="D10" s="9"/>
       <c r="E10" s="10"/>
-      <c r="F10" s="36"/>
+      <c r="F10" s="37"/>
       <c r="G10" s="10"/>
       <c r="H10" s="11"/>
       <c r="I10" s="12"/>
@@ -2088,7 +2061,7 @@
       <c r="W10" s="18"/>
       <c r="X10" s="12"/>
       <c r="Y10" s="19"/>
-      <c r="AA10" s="37"/>
+      <c r="AA10" s="38"/>
       <c r="AC10" s="22"/>
       <c r="AE10" s="14"/>
       <c r="AG10" s="35"/>
@@ -2123,13 +2096,13 @@
       <c r="BL10" s="30"/>
       <c r="BM10" s="30"/>
     </row>
-    <row r="11" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="33"/>
       <c r="B11" s="33"/>
       <c r="C11" s="8"/>
       <c r="D11" s="9"/>
       <c r="E11" s="10"/>
-      <c r="F11" s="36"/>
+      <c r="F11" s="37"/>
       <c r="G11" s="10"/>
       <c r="H11" s="11"/>
       <c r="I11" s="12"/>
@@ -2184,13 +2157,13 @@
       <c r="BL11" s="30"/>
       <c r="BM11" s="30"/>
     </row>
-    <row r="12" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="33"/>
       <c r="B12" s="33"/>
       <c r="C12" s="8"/>
       <c r="D12" s="9"/>
       <c r="E12" s="10"/>
-      <c r="F12" s="36"/>
+      <c r="F12" s="37"/>
       <c r="G12" s="10"/>
       <c r="H12" s="11"/>
       <c r="I12" s="12"/>
@@ -2210,7 +2183,7 @@
       <c r="W12" s="18"/>
       <c r="X12" s="12"/>
       <c r="Y12" s="19"/>
-      <c r="Z12" s="38"/>
+      <c r="Z12" s="39"/>
       <c r="AA12" s="21"/>
       <c r="AC12" s="22"/>
       <c r="AE12" s="14"/>
@@ -2246,13 +2219,13 @@
       <c r="BL12" s="30"/>
       <c r="BM12" s="30"/>
     </row>
-    <row r="13" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="33"/>
       <c r="B13" s="33"/>
       <c r="C13" s="8"/>
       <c r="D13" s="9"/>
       <c r="E13" s="10"/>
-      <c r="F13" s="36"/>
+      <c r="F13" s="37"/>
       <c r="G13" s="10"/>
       <c r="H13" s="11"/>
       <c r="I13" s="12"/>
@@ -2272,9 +2245,9 @@
       <c r="W13" s="18"/>
       <c r="X13" s="12"/>
       <c r="Y13" s="19"/>
-      <c r="Z13" s="38"/>
+      <c r="Z13" s="39"/>
       <c r="AA13" s="21"/>
-      <c r="AB13" s="38"/>
+      <c r="AB13" s="39"/>
       <c r="AC13" s="22"/>
       <c r="AE13" s="14"/>
       <c r="AG13" s="35"/>
@@ -2309,80 +2282,80 @@
       <c r="BL13" s="30"/>
       <c r="BM13" s="30"/>
     </row>
-    <row r="14" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="33"/>
       <c r="B14" s="33"/>
       <c r="C14" s="8"/>
       <c r="D14" s="9"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="36"/>
+      <c r="E14" s="40"/>
+      <c r="F14" s="37"/>
       <c r="G14" s="10"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="41"/>
-      <c r="J14" s="41"/>
-      <c r="K14" s="41"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="42"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="42"/>
       <c r="L14" s="18"/>
-      <c r="M14" s="42"/>
-      <c r="N14" s="43"/>
-      <c r="O14" s="41"/>
+      <c r="M14" s="43"/>
+      <c r="N14" s="44"/>
+      <c r="O14" s="42"/>
       <c r="P14" s="12"/>
-      <c r="Q14" s="43"/>
-      <c r="R14" s="41"/>
-      <c r="S14" s="41"/>
-      <c r="T14" s="44"/>
-      <c r="U14" s="45"/>
-      <c r="V14" s="41"/>
+      <c r="Q14" s="44"/>
+      <c r="R14" s="42"/>
+      <c r="S14" s="42"/>
+      <c r="T14" s="45"/>
+      <c r="U14" s="46"/>
+      <c r="V14" s="42"/>
       <c r="W14" s="18"/>
-      <c r="X14" s="41"/>
-      <c r="Y14" s="46"/>
+      <c r="X14" s="42"/>
+      <c r="Y14" s="47"/>
       <c r="Z14" s="35"/>
-      <c r="AA14" s="47"/>
+      <c r="AA14" s="48"/>
       <c r="AB14" s="35"/>
-      <c r="AC14" s="48"/>
+      <c r="AC14" s="49"/>
       <c r="AD14" s="35"/>
-      <c r="AE14" s="42"/>
+      <c r="AE14" s="43"/>
       <c r="AF14" s="35"/>
       <c r="AG14" s="35"/>
-      <c r="AH14" s="41"/>
+      <c r="AH14" s="42"/>
       <c r="AI14" s="25"/>
-      <c r="AJ14" s="49"/>
-      <c r="AK14" s="41"/>
-      <c r="AL14" s="44"/>
-      <c r="AM14" s="50"/>
-      <c r="AN14" s="50"/>
+      <c r="AJ14" s="50"/>
+      <c r="AK14" s="42"/>
+      <c r="AL14" s="45"/>
+      <c r="AM14" s="51"/>
+      <c r="AN14" s="51"/>
       <c r="AO14" s="14"/>
       <c r="AP14" s="15"/>
       <c r="AQ14" s="16"/>
       <c r="AR14" s="24"/>
-      <c r="AS14" s="51"/>
+      <c r="AS14" s="52"/>
       <c r="AT14" s="35"/>
       <c r="AU14" s="18"/>
-      <c r="AV14" s="52"/>
-      <c r="AW14" s="52"/>
-      <c r="AX14" s="52"/>
-      <c r="AY14" s="52"/>
-      <c r="AZ14" s="53"/>
-      <c r="BA14" s="52"/>
-      <c r="BB14" s="54"/>
-      <c r="BC14" s="54"/>
+      <c r="AV14" s="53"/>
+      <c r="AW14" s="53"/>
+      <c r="AX14" s="53"/>
+      <c r="AY14" s="53"/>
+      <c r="AZ14" s="54"/>
+      <c r="BA14" s="53"/>
+      <c r="BB14" s="55"/>
+      <c r="BC14" s="55"/>
       <c r="BD14" s="31"/>
-      <c r="BE14" s="54"/>
-      <c r="BF14" s="54"/>
+      <c r="BE14" s="55"/>
+      <c r="BF14" s="55"/>
       <c r="BG14" s="32"/>
-      <c r="BH14" s="54"/>
-      <c r="BI14" s="54"/>
-      <c r="BJ14" s="54"/>
+      <c r="BH14" s="55"/>
+      <c r="BI14" s="55"/>
+      <c r="BJ14" s="55"/>
       <c r="BK14" s="30"/>
       <c r="BL14" s="30"/>
       <c r="BM14" s="30"/>
     </row>
-    <row r="15" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="33"/>
       <c r="B15" s="33"/>
       <c r="C15" s="8"/>
       <c r="D15" s="9"/>
       <c r="E15" s="10"/>
-      <c r="F15" s="36"/>
+      <c r="F15" s="37"/>
       <c r="G15" s="10"/>
       <c r="H15" s="11"/>
       <c r="I15" s="12"/>
@@ -2438,13 +2411,13 @@
       <c r="BL15" s="30"/>
       <c r="BM15" s="30"/>
     </row>
-    <row r="16" spans="1:65" s="2" customFormat="1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="33"/>
       <c r="B16" s="33"/>
       <c r="C16" s="8"/>
       <c r="D16" s="9"/>
       <c r="E16" s="10"/>
-      <c r="F16" s="36"/>
+      <c r="F16" s="37"/>
       <c r="G16" s="10"/>
       <c r="H16" s="11"/>
       <c r="I16" s="12"/>
@@ -2464,7 +2437,7 @@
       <c r="W16" s="18"/>
       <c r="X16" s="12"/>
       <c r="Y16" s="19"/>
-      <c r="Z16" s="38"/>
+      <c r="Z16" s="39"/>
       <c r="AA16" s="21"/>
       <c r="AC16" s="22"/>
       <c r="AE16" s="14"/>
@@ -2500,9 +2473,9 @@
       <c r="BL16" s="30"/>
       <c r="BM16" s="30"/>
     </row>
-    <row r="17" spans="1:78" s="2" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" spans="1:78" s="2" customFormat="1" ht="13.8" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="13.75" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="18" ht="13.75" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="19" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -2582,7 +2555,7 @@
       <c r="BY19" s="2"/>
       <c r="BZ19" s="2"/>
     </row>
-    <row r="20" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -2662,7 +2635,7 @@
       <c r="BY20" s="2"/>
       <c r="BZ20" s="2"/>
     </row>
-    <row r="21" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -2742,7 +2715,7 @@
       <c r="BY21" s="2"/>
       <c r="BZ21" s="2"/>
     </row>
-    <row r="22" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -2822,7 +2795,7 @@
       <c r="BY22" s="2"/>
       <c r="BZ22" s="2"/>
     </row>
-    <row r="23" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -2902,7 +2875,7 @@
       <c r="BY23" s="2"/>
       <c r="BZ23" s="2"/>
     </row>
-    <row r="24" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -2982,7 +2955,7 @@
       <c r="BY24" s="2"/>
       <c r="BZ24" s="2"/>
     </row>
-    <row r="25" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -3062,7 +3035,7 @@
       <c r="BY25" s="2"/>
       <c r="BZ25" s="2"/>
     </row>
-    <row r="26" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -3142,7 +3115,7 @@
       <c r="BY26" s="2"/>
       <c r="BZ26" s="2"/>
     </row>
-    <row r="27" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -3222,7 +3195,7 @@
       <c r="BY27" s="2"/>
       <c r="BZ27" s="2"/>
     </row>
-    <row r="28" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -3302,7 +3275,7 @@
       <c r="BY28" s="2"/>
       <c r="BZ28" s="2"/>
     </row>
-    <row r="29" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="29" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -3382,7 +3355,7 @@
       <c r="BY29" s="2"/>
       <c r="BZ29" s="2"/>
     </row>
-    <row r="30" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="30" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -3462,7 +3435,7 @@
       <c r="BY30" s="2"/>
       <c r="BZ30" s="2"/>
     </row>
-    <row r="31" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="31" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -3542,7 +3515,7 @@
       <c r="BY31" s="2"/>
       <c r="BZ31" s="2"/>
     </row>
-    <row r="32" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -3622,7 +3595,7 @@
       <c r="BY32" s="2"/>
       <c r="BZ32" s="2"/>
     </row>
-    <row r="33" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="33" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -3702,7 +3675,7 @@
       <c r="BY33" s="2"/>
       <c r="BZ33" s="2"/>
     </row>
-    <row r="34" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -3782,7 +3755,7 @@
       <c r="BY34" s="2"/>
       <c r="BZ34" s="2"/>
     </row>
-    <row r="35" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="35" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -3862,7 +3835,7 @@
       <c r="BY35" s="2"/>
       <c r="BZ35" s="2"/>
     </row>
-    <row r="36" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="36" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -3942,7 +3915,7 @@
       <c r="BY36" s="2"/>
       <c r="BZ36" s="2"/>
     </row>
-    <row r="37" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="37" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -4022,7 +3995,7 @@
       <c r="BY37" s="2"/>
       <c r="BZ37" s="2"/>
     </row>
-    <row r="38" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="38" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -4102,7 +4075,7 @@
       <c r="BY38" s="2"/>
       <c r="BZ38" s="2"/>
     </row>
-    <row r="39" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="39" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -4182,7 +4155,7 @@
       <c r="BY39" s="2"/>
       <c r="BZ39" s="2"/>
     </row>
-    <row r="40" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="40" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -4262,7 +4235,7 @@
       <c r="BY40" s="2"/>
       <c r="BZ40" s="2"/>
     </row>
-    <row r="41" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="41" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -4342,7 +4315,7 @@
       <c r="BY41" s="2"/>
       <c r="BZ41" s="2"/>
     </row>
-    <row r="42" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -4422,7 +4395,7 @@
       <c r="BY42" s="2"/>
       <c r="BZ42" s="2"/>
     </row>
-    <row r="43" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="43" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -4502,7 +4475,7 @@
       <c r="BY43" s="2"/>
       <c r="BZ43" s="2"/>
     </row>
-    <row r="44" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="44" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -4582,7 +4555,7 @@
       <c r="BY44" s="2"/>
       <c r="BZ44" s="2"/>
     </row>
-    <row r="45" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="45" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -4662,7 +4635,7 @@
       <c r="BY45" s="2"/>
       <c r="BZ45" s="2"/>
     </row>
-    <row r="46" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="46" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -4742,7 +4715,7 @@
       <c r="BY46" s="2"/>
       <c r="BZ46" s="2"/>
     </row>
-    <row r="47" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="47" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -4822,7 +4795,7 @@
       <c r="BY47" s="2"/>
       <c r="BZ47" s="2"/>
     </row>
-    <row r="48" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="48" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -4902,7 +4875,7 @@
       <c r="BY48" s="2"/>
       <c r="BZ48" s="2"/>
     </row>
-    <row r="49" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="49" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -4982,7 +4955,7 @@
       <c r="BY49" s="2"/>
       <c r="BZ49" s="2"/>
     </row>
-    <row r="50" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="50" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -5062,7 +5035,7 @@
       <c r="BY50" s="2"/>
       <c r="BZ50" s="2"/>
     </row>
-    <row r="51" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="51" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -5142,7 +5115,7 @@
       <c r="BY51" s="2"/>
       <c r="BZ51" s="2"/>
     </row>
-    <row r="52" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="52" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -5222,7 +5195,7 @@
       <c r="BY52" s="2"/>
       <c r="BZ52" s="2"/>
     </row>
-    <row r="53" spans="1:78" s="38" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="53" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
@@ -5302,7 +5275,7 @@
       <c r="BY53" s="2"/>
       <c r="BZ53" s="2"/>
     </row>
-    <row r="54" spans="1:78" x14ac:dyDescent="0.3">
+    <row r="54" ht="14.5" customHeight="1" spans="1:78" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
@@ -5383,18 +5356,66 @@
       <c r="BZ54" s="2"/>
     </row>
   </sheetData>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AM10:AM16 X10:X16 V10:V16 R10:S16 J10:K16 BI10:BI16 BC10:BC16 AY10:AY16 AP10:AP16" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="18">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AM10:AM16">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AM2:AM16 X2:X16 V2:V16 R2:S16 J2:K16 BI2:BI16 BC2:BC16 AY2:AY16 AP2:AP16" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AM2:AM16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AP10:AP16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AP2:AP16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY10:AY16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AY2:AY16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC10:BC16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC2:BC16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BI10:BI16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BI2:BI16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J10:K16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J2:K16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R10:S16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2:S16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V10:V16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V2:V16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X10:X16">
+      <formula1>INDIRECT($E2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X16">
       <formula1>INDIRECT($E2)</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="U2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="U2" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId2"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/Data/Hires/Workday_NewHire_Spain_Regression_PK17.xlsx
+++ b/Data/Hires/Workday_NewHire_Spain_Regression_PK17.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="121">
   <si>
     <t>TestCaseIDs</t>
   </si>
@@ -208,16 +208,13 @@
     <t>Test_1</t>
   </si>
   <si>
-    <t>10700263</t>
-  </si>
-  <si>
     <t>Passed</t>
   </si>
   <si>
     <t>356 Recruitment (Posob Zujefy Pyronu (2577) (Inherited))</t>
   </si>
   <si>
-    <t>FourteenJuly</t>
+    <t>FourAugust</t>
   </si>
   <si>
     <t>NEWHIRE</t>
@@ -319,7 +316,7 @@
     <t>ID Card (DNI) Number</t>
   </si>
   <si>
-    <t>10006628A</t>
+    <t>10006639A</t>
   </si>
   <si>
     <t>BBVAESMM111</t>
@@ -340,19 +337,22 @@
     <t>Test_2</t>
   </si>
   <si>
-    <t>10700264</t>
+    <t>10700476</t>
   </si>
   <si>
     <t>365 Store Management (Cisuw Hapagu Pahame (10274587))</t>
   </si>
   <si>
-    <t>NEWHIREMANAGER</t>
+    <t>EightAugustNewManger</t>
+  </si>
+  <si>
+    <t>NewManger</t>
   </si>
   <si>
     <t>SLNameTwoo</t>
   </si>
   <si>
-    <t>Auto 62179809</t>
+    <t>Auto 39553277</t>
   </si>
   <si>
     <t>Permanent</t>
@@ -377,7 +377,7 @@
 </t>
   </si>
   <si>
-    <t>10006629A</t>
+    <t>10006648A</t>
   </si>
   <si>
     <t>54 - ENSEÑANZAS UNIVERSITARIAS DE PRIMER CICLO Y EQUIVALENTES</t>
@@ -483,7 +483,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -509,7 +509,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -522,6 +523,11 @@
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.7999816888943144"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -555,7 +561,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -649,6 +655,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -995,8 +1004,8 @@
     <col min="1" max="1" width="11.36328125" customWidth="1"/>
     <col min="2" max="2" width="51.36328125" customWidth="1"/>
     <col min="3" max="3" width="10.1796875" customWidth="1"/>
-    <col min="4" max="4" width="41.453125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
+    <col min="4" max="4" width="54.7265625" customWidth="1"/>
+    <col min="5" max="5" width="32.26953125" customWidth="1"/>
     <col min="6" max="6" width="13.453125" customWidth="1"/>
     <col min="7" max="7" width="21.81640625" customWidth="1"/>
     <col min="8" max="8" width="13.453125" customWidth="1"/>
@@ -1271,219 +1280,219 @@
       <c r="A2" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="7">
+        <v>10700463</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="D2" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="E2" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="F2" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="G2" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="H2" s="11" t="s">
         <v>68</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>69</v>
       </c>
       <c r="I2" s="12">
         <v>919193394</v>
       </c>
       <c r="J2" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="K2" s="12" t="s">
         <v>70</v>
-      </c>
-      <c r="K2" s="12" t="s">
-        <v>71</v>
       </c>
       <c r="L2" s="13">
         <f t="shared" ref="L2" si="0">TODAY()-7</f>
-        <v>45845</v>
+        <v>45870</v>
       </c>
       <c r="M2" s="14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N2" s="15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O2" s="12">
         <v>44</v>
       </c>
       <c r="P2" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="Q2" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="Q2" s="15" t="s">
+      <c r="R2" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="S2" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="T2" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="R2" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="S2" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="T2" s="16" t="s">
+      <c r="U2" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="U2" s="17" t="s">
-        <v>76</v>
-      </c>
       <c r="V2" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="W2" s="18">
         <f t="shared" ref="W2" si="1">TODAY()-7</f>
-        <v>45845</v>
+        <v>45870</v>
       </c>
       <c r="X2" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y2" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="Y2" s="19" t="s">
+      <c r="Z2" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="Z2" s="20" t="s">
+      <c r="AA2" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="AA2" s="21" t="s">
+      <c r="AB2" t="s">
         <v>80</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>81</v>
       </c>
       <c r="AC2" s="22">
         <v>356</v>
       </c>
       <c r="AD2" s="23" t="s">
+        <v>81</v>
+      </c>
+      <c r="AE2" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="AE2" s="14" t="s">
+      <c r="AF2" t="s">
         <v>83</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>84</v>
       </c>
       <c r="AG2" s="24">
         <f>TODAY()+365</f>
-        <v>46217</v>
+        <v>46242</v>
       </c>
       <c r="AH2" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="AI2" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="AI2" s="25" t="s">
+      <c r="AJ2" t="s">
         <v>86</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AK2" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="AK2" s="12" t="s">
+      <c r="AL2" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="AL2" s="16" t="s">
+      <c r="AM2" s="26" t="s">
         <v>89</v>
-      </c>
-      <c r="AM2" s="26" t="s">
-        <v>90</v>
       </c>
       <c r="AN2" s="26">
         <f t="shared" ref="AN2" si="2">TODAY()+7</f>
-        <v>45859</v>
+        <v>45884</v>
       </c>
       <c r="AO2" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP2" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="AP2" s="15" t="s">
+      <c r="AQ2" s="16" t="s">
         <v>92</v>
-      </c>
-      <c r="AQ2" s="16" t="s">
-        <v>93</v>
       </c>
       <c r="AR2" s="24">
         <f t="shared" ref="AR2" si="3">TODAY()+365</f>
-        <v>46217</v>
+        <v>46242</v>
       </c>
       <c r="AS2" s="27" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AT2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AU2" s="13">
         <v>29221</v>
       </c>
       <c r="AV2" s="28" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AW2" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="AX2" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="AY2" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="AX2" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="AY2" s="28" t="s">
+      <c r="AZ2" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="AZ2" s="29" t="s">
+      <c r="BA2" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="BB2" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="BC2" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="BA2" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="BB2" s="30" t="s">
-        <v>69</v>
-      </c>
-      <c r="BC2" s="30" t="s">
+      <c r="BD2" s="31">
+        <v>281000758119</v>
+      </c>
+      <c r="BE2" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="BF2" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="BD2" s="31">
-        <v>281000758106</v>
-      </c>
-      <c r="BE2" s="30" t="s">
-        <v>69</v>
-      </c>
-      <c r="BF2" s="30" t="s">
+      <c r="BG2" s="32" t="s">
         <v>99</v>
       </c>
-      <c r="BG2" s="32" t="s">
+      <c r="BH2" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="BH2" s="30" t="s">
+      <c r="BI2" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="BI2" s="30" t="s">
+      <c r="BJ2" s="30" t="s">
         <v>102</v>
       </c>
-      <c r="BJ2" s="30" t="s">
+      <c r="BK2" s="30" t="s">
         <v>103</v>
-      </c>
-      <c r="BK2" s="30" t="s">
-        <v>104</v>
       </c>
       <c r="BL2" s="30">
         <v>36526</v>
       </c>
       <c r="BM2" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="33" t="s">
+        <v>105</v>
+      </c>
+      <c r="B3" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="B3" s="34" t="s">
+      <c r="C3" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="D3" s="9" t="s">
+      <c r="E3" s="10" t="s">
         <v>108</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>66</v>
       </c>
       <c r="F3" s="10" t="s">
         <v>109</v>
@@ -1492,25 +1501,25 @@
         <v>110</v>
       </c>
       <c r="H3" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I3" s="12">
         <v>919193436</v>
       </c>
       <c r="J3" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="K3" s="12" t="s">
         <v>70</v>
-      </c>
-      <c r="K3" s="12" t="s">
-        <v>71</v>
       </c>
       <c r="L3" s="13">
         <v>45800</v>
       </c>
       <c r="M3" s="14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N3" s="15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O3" s="12">
         <v>44</v>
@@ -1519,28 +1528,28 @@
         <v>28013</v>
       </c>
       <c r="Q3" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="R3" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="S3" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="T3" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="R3" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="S3" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="T3" s="16" t="s">
+      <c r="U3" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="U3" s="15" t="s">
-        <v>76</v>
-      </c>
       <c r="V3" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="W3" s="18">
         <v>45800</v>
       </c>
       <c r="X3" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Y3" s="19" t="s">
         <v>111</v>
@@ -1561,16 +1570,16 @@
         <v>100</v>
       </c>
       <c r="AE3" s="14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AF3" t="s">
         <v>115</v>
       </c>
-      <c r="AG3" s="35" t="s">
-        <v>78</v>
+      <c r="AG3" s="36" t="s">
+        <v>77</v>
       </c>
       <c r="AH3" s="12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AI3" s="25" t="s">
         <v>116</v>
@@ -1579,82 +1588,82 @@
         <v>117</v>
       </c>
       <c r="AK3" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="AL3" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="AL3" s="37" t="s">
         <v>118</v>
       </c>
       <c r="AM3" s="26" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AN3" s="26">
         <v>45814</v>
       </c>
       <c r="AO3" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="AP3" s="15" t="s">
         <v>91</v>
       </c>
-      <c r="AP3" s="15" t="s">
+      <c r="AQ3" s="16" t="s">
         <v>92</v>
-      </c>
-      <c r="AQ3" s="16" t="s">
-        <v>93</v>
       </c>
       <c r="AR3" s="24">
         <v>46172</v>
       </c>
       <c r="AS3" s="27" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AT3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AU3" s="13">
         <v>29221</v>
       </c>
       <c r="AV3" s="28" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AW3" s="28" t="s">
+        <v>94</v>
+      </c>
+      <c r="AX3" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="AY3" s="28" t="s">
         <v>95</v>
-      </c>
-      <c r="AX3" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="AY3" s="28" t="s">
-        <v>96</v>
       </c>
       <c r="AZ3" s="29">
         <v>40844</v>
       </c>
       <c r="BA3" s="28" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="BB3" s="30" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="BC3" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="BD3" s="31">
+        <v>281000758128</v>
+      </c>
+      <c r="BE3" s="30" t="s">
+        <v>68</v>
+      </c>
+      <c r="BF3" s="30" t="s">
         <v>98</v>
-      </c>
-      <c r="BD3" s="31">
-        <v>281000758107</v>
-      </c>
-      <c r="BE3" s="30" t="s">
-        <v>69</v>
-      </c>
-      <c r="BF3" s="30" t="s">
-        <v>99</v>
       </c>
       <c r="BG3" s="32" t="s">
         <v>119</v>
       </c>
       <c r="BH3" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="BI3" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="BI3" s="30" t="s">
+      <c r="BJ3" s="30" t="s">
         <v>102</v>
-      </c>
-      <c r="BJ3" s="30" t="s">
-        <v>103</v>
       </c>
       <c r="BK3" s="30" t="s">
         <v>120</v>
@@ -1663,16 +1672,16 @@
         <v>36526</v>
       </c>
       <c r="BM3" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="33"/>
       <c r="B4" s="6"/>
-      <c r="C4" s="8"/>
+      <c r="C4" s="33"/>
       <c r="D4" s="9"/>
       <c r="E4" s="10"/>
-      <c r="F4" s="37"/>
+      <c r="F4" s="38"/>
       <c r="G4" s="10"/>
       <c r="H4" s="11"/>
       <c r="I4" s="12"/>
@@ -1695,7 +1704,7 @@
       <c r="AA4" s="21"/>
       <c r="AC4" s="22"/>
       <c r="AE4" s="14"/>
-      <c r="AG4" s="35"/>
+      <c r="AG4" s="36"/>
       <c r="AH4" s="12"/>
       <c r="AI4" s="25"/>
       <c r="AK4" s="12"/>
@@ -1730,10 +1739,10 @@
     <row r="5" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="33"/>
       <c r="B5" s="33"/>
-      <c r="C5" s="8"/>
+      <c r="C5" s="33"/>
       <c r="D5" s="9"/>
       <c r="E5" s="10"/>
-      <c r="F5" s="37"/>
+      <c r="F5" s="38"/>
       <c r="G5" s="10"/>
       <c r="H5" s="11"/>
       <c r="I5" s="12"/>
@@ -1757,7 +1766,7 @@
       <c r="AC5" s="22"/>
       <c r="AD5" s="23"/>
       <c r="AE5" s="14"/>
-      <c r="AG5" s="35"/>
+      <c r="AG5" s="36"/>
       <c r="AH5" s="12"/>
       <c r="AI5" s="25"/>
       <c r="AK5" s="12"/>
@@ -1792,10 +1801,10 @@
     <row r="6" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="33"/>
       <c r="B6" s="33"/>
-      <c r="C6" s="8"/>
+      <c r="C6" s="33"/>
       <c r="D6" s="9"/>
       <c r="E6" s="10"/>
-      <c r="F6" s="37"/>
+      <c r="F6" s="38"/>
       <c r="G6" s="10"/>
       <c r="H6" s="11"/>
       <c r="I6" s="12"/>
@@ -1854,10 +1863,10 @@
     <row r="7" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="33"/>
       <c r="B7" s="33"/>
-      <c r="C7" s="8"/>
+      <c r="C7" s="33"/>
       <c r="D7" s="9"/>
       <c r="E7" s="10"/>
-      <c r="F7" s="37"/>
+      <c r="F7" s="38"/>
       <c r="G7" s="10"/>
       <c r="H7" s="11"/>
       <c r="I7" s="12"/>
@@ -1880,7 +1889,7 @@
       <c r="AA7" s="21"/>
       <c r="AC7" s="22"/>
       <c r="AE7" s="14"/>
-      <c r="AG7" s="35"/>
+      <c r="AG7" s="36"/>
       <c r="AH7" s="12"/>
       <c r="AI7" s="25"/>
       <c r="AK7" s="12"/>
@@ -1915,10 +1924,10 @@
     <row r="8" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="33"/>
       <c r="B8" s="33"/>
-      <c r="C8" s="8"/>
+      <c r="C8" s="33"/>
       <c r="D8" s="9"/>
       <c r="E8" s="10"/>
-      <c r="F8" s="37"/>
+      <c r="F8" s="38"/>
       <c r="G8" s="10"/>
       <c r="H8" s="11"/>
       <c r="I8" s="12"/>
@@ -1941,7 +1950,7 @@
       <c r="AA8" s="21"/>
       <c r="AC8" s="22"/>
       <c r="AE8" s="14"/>
-      <c r="AG8" s="35"/>
+      <c r="AG8" s="36"/>
       <c r="AH8" s="12"/>
       <c r="AI8" s="25"/>
       <c r="AK8" s="12"/>
@@ -1976,10 +1985,10 @@
     <row r="9" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="33"/>
       <c r="B9" s="33"/>
-      <c r="C9" s="8"/>
+      <c r="C9" s="33"/>
       <c r="D9" s="9"/>
       <c r="E9" s="10"/>
-      <c r="F9" s="37"/>
+      <c r="F9" s="38"/>
       <c r="G9" s="10"/>
       <c r="H9" s="11"/>
       <c r="I9" s="12"/>
@@ -2038,10 +2047,10 @@
     <row r="10" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="33"/>
       <c r="B10" s="33"/>
-      <c r="C10" s="8"/>
+      <c r="C10" s="33"/>
       <c r="D10" s="9"/>
       <c r="E10" s="10"/>
-      <c r="F10" s="37"/>
+      <c r="F10" s="38"/>
       <c r="G10" s="10"/>
       <c r="H10" s="11"/>
       <c r="I10" s="12"/>
@@ -2061,10 +2070,10 @@
       <c r="W10" s="18"/>
       <c r="X10" s="12"/>
       <c r="Y10" s="19"/>
-      <c r="AA10" s="38"/>
+      <c r="AA10" s="39"/>
       <c r="AC10" s="22"/>
       <c r="AE10" s="14"/>
-      <c r="AG10" s="35"/>
+      <c r="AG10" s="36"/>
       <c r="AH10" s="12"/>
       <c r="AI10" s="25"/>
       <c r="AK10" s="12"/>
@@ -2099,10 +2108,10 @@
     <row r="11" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="33"/>
       <c r="B11" s="33"/>
-      <c r="C11" s="8"/>
+      <c r="C11" s="33"/>
       <c r="D11" s="9"/>
       <c r="E11" s="10"/>
-      <c r="F11" s="37"/>
+      <c r="F11" s="38"/>
       <c r="G11" s="10"/>
       <c r="H11" s="11"/>
       <c r="I11" s="12"/>
@@ -2125,7 +2134,7 @@
       <c r="AA11" s="21"/>
       <c r="AC11" s="22"/>
       <c r="AE11" s="14"/>
-      <c r="AG11" s="35"/>
+      <c r="AG11" s="36"/>
       <c r="AH11" s="12"/>
       <c r="AI11" s="25"/>
       <c r="AK11" s="12"/>
@@ -2160,10 +2169,10 @@
     <row r="12" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="33"/>
       <c r="B12" s="33"/>
-      <c r="C12" s="8"/>
+      <c r="C12" s="33"/>
       <c r="D12" s="9"/>
       <c r="E12" s="10"/>
-      <c r="F12" s="37"/>
+      <c r="F12" s="38"/>
       <c r="G12" s="10"/>
       <c r="H12" s="11"/>
       <c r="I12" s="12"/>
@@ -2183,7 +2192,7 @@
       <c r="W12" s="18"/>
       <c r="X12" s="12"/>
       <c r="Y12" s="19"/>
-      <c r="Z12" s="39"/>
+      <c r="Z12" s="40"/>
       <c r="AA12" s="21"/>
       <c r="AC12" s="22"/>
       <c r="AE12" s="14"/>
@@ -2222,10 +2231,10 @@
     <row r="13" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="33"/>
       <c r="B13" s="33"/>
-      <c r="C13" s="8"/>
+      <c r="C13" s="33"/>
       <c r="D13" s="9"/>
       <c r="E13" s="10"/>
-      <c r="F13" s="37"/>
+      <c r="F13" s="38"/>
       <c r="G13" s="10"/>
       <c r="H13" s="11"/>
       <c r="I13" s="12"/>
@@ -2245,12 +2254,12 @@
       <c r="W13" s="18"/>
       <c r="X13" s="12"/>
       <c r="Y13" s="19"/>
-      <c r="Z13" s="39"/>
+      <c r="Z13" s="40"/>
       <c r="AA13" s="21"/>
-      <c r="AB13" s="39"/>
+      <c r="AB13" s="40"/>
       <c r="AC13" s="22"/>
       <c r="AE13" s="14"/>
-      <c r="AG13" s="35"/>
+      <c r="AG13" s="36"/>
       <c r="AH13" s="12"/>
       <c r="AI13" s="25"/>
       <c r="AK13" s="12"/>
@@ -2285,66 +2294,66 @@
     <row r="14" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="33"/>
       <c r="B14" s="33"/>
-      <c r="C14" s="8"/>
+      <c r="C14" s="33"/>
       <c r="D14" s="9"/>
-      <c r="E14" s="40"/>
-      <c r="F14" s="37"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="38"/>
       <c r="G14" s="10"/>
-      <c r="H14" s="41"/>
-      <c r="I14" s="42"/>
-      <c r="J14" s="42"/>
-      <c r="K14" s="42"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="43"/>
+      <c r="J14" s="43"/>
+      <c r="K14" s="43"/>
       <c r="L14" s="18"/>
-      <c r="M14" s="43"/>
-      <c r="N14" s="44"/>
-      <c r="O14" s="42"/>
+      <c r="M14" s="44"/>
+      <c r="N14" s="45"/>
+      <c r="O14" s="43"/>
       <c r="P14" s="12"/>
-      <c r="Q14" s="44"/>
-      <c r="R14" s="42"/>
-      <c r="S14" s="42"/>
-      <c r="T14" s="45"/>
-      <c r="U14" s="46"/>
-      <c r="V14" s="42"/>
+      <c r="Q14" s="45"/>
+      <c r="R14" s="43"/>
+      <c r="S14" s="43"/>
+      <c r="T14" s="46"/>
+      <c r="U14" s="47"/>
+      <c r="V14" s="43"/>
       <c r="W14" s="18"/>
-      <c r="X14" s="42"/>
-      <c r="Y14" s="47"/>
-      <c r="Z14" s="35"/>
-      <c r="AA14" s="48"/>
-      <c r="AB14" s="35"/>
-      <c r="AC14" s="49"/>
-      <c r="AD14" s="35"/>
-      <c r="AE14" s="43"/>
-      <c r="AF14" s="35"/>
-      <c r="AG14" s="35"/>
-      <c r="AH14" s="42"/>
+      <c r="X14" s="43"/>
+      <c r="Y14" s="48"/>
+      <c r="Z14" s="36"/>
+      <c r="AA14" s="49"/>
+      <c r="AB14" s="36"/>
+      <c r="AC14" s="50"/>
+      <c r="AD14" s="36"/>
+      <c r="AE14" s="44"/>
+      <c r="AF14" s="36"/>
+      <c r="AG14" s="36"/>
+      <c r="AH14" s="43"/>
       <c r="AI14" s="25"/>
-      <c r="AJ14" s="50"/>
-      <c r="AK14" s="42"/>
-      <c r="AL14" s="45"/>
-      <c r="AM14" s="51"/>
-      <c r="AN14" s="51"/>
+      <c r="AJ14" s="51"/>
+      <c r="AK14" s="43"/>
+      <c r="AL14" s="46"/>
+      <c r="AM14" s="52"/>
+      <c r="AN14" s="52"/>
       <c r="AO14" s="14"/>
       <c r="AP14" s="15"/>
       <c r="AQ14" s="16"/>
       <c r="AR14" s="24"/>
-      <c r="AS14" s="52"/>
-      <c r="AT14" s="35"/>
+      <c r="AS14" s="53"/>
+      <c r="AT14" s="36"/>
       <c r="AU14" s="18"/>
-      <c r="AV14" s="53"/>
-      <c r="AW14" s="53"/>
-      <c r="AX14" s="53"/>
-      <c r="AY14" s="53"/>
-      <c r="AZ14" s="54"/>
-      <c r="BA14" s="53"/>
-      <c r="BB14" s="55"/>
-      <c r="BC14" s="55"/>
+      <c r="AV14" s="54"/>
+      <c r="AW14" s="54"/>
+      <c r="AX14" s="54"/>
+      <c r="AY14" s="54"/>
+      <c r="AZ14" s="55"/>
+      <c r="BA14" s="54"/>
+      <c r="BB14" s="56"/>
+      <c r="BC14" s="56"/>
       <c r="BD14" s="31"/>
-      <c r="BE14" s="55"/>
-      <c r="BF14" s="55"/>
+      <c r="BE14" s="56"/>
+      <c r="BF14" s="56"/>
       <c r="BG14" s="32"/>
-      <c r="BH14" s="55"/>
-      <c r="BI14" s="55"/>
-      <c r="BJ14" s="55"/>
+      <c r="BH14" s="56"/>
+      <c r="BI14" s="56"/>
+      <c r="BJ14" s="56"/>
       <c r="BK14" s="30"/>
       <c r="BL14" s="30"/>
       <c r="BM14" s="30"/>
@@ -2352,10 +2361,10 @@
     <row r="15" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="33"/>
       <c r="B15" s="33"/>
-      <c r="C15" s="8"/>
+      <c r="C15" s="33"/>
       <c r="D15" s="9"/>
       <c r="E15" s="10"/>
-      <c r="F15" s="37"/>
+      <c r="F15" s="38"/>
       <c r="G15" s="10"/>
       <c r="H15" s="11"/>
       <c r="I15" s="12"/>
@@ -2414,10 +2423,10 @@
     <row r="16" ht="17.4" customHeight="1" spans="1:65" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="33"/>
       <c r="B16" s="33"/>
-      <c r="C16" s="8"/>
+      <c r="C16" s="33"/>
       <c r="D16" s="9"/>
       <c r="E16" s="10"/>
-      <c r="F16" s="37"/>
+      <c r="F16" s="38"/>
       <c r="G16" s="10"/>
       <c r="H16" s="11"/>
       <c r="I16" s="12"/>
@@ -2437,11 +2446,11 @@
       <c r="W16" s="18"/>
       <c r="X16" s="12"/>
       <c r="Y16" s="19"/>
-      <c r="Z16" s="39"/>
+      <c r="Z16" s="40"/>
       <c r="AA16" s="21"/>
       <c r="AC16" s="22"/>
       <c r="AE16" s="14"/>
-      <c r="AG16" s="35"/>
+      <c r="AG16" s="36"/>
       <c r="AH16" s="12"/>
       <c r="AI16" s="25"/>
       <c r="AK16" s="12"/>
@@ -2475,7 +2484,7 @@
     </row>
     <row r="17" ht="13.75" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
     <row r="18" ht="13.75" customHeight="1" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="19" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
@@ -2555,7 +2564,7 @@
       <c r="BY19" s="2"/>
       <c r="BZ19" s="2"/>
     </row>
-    <row r="20" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -2635,7 +2644,7 @@
       <c r="BY20" s="2"/>
       <c r="BZ20" s="2"/>
     </row>
-    <row r="21" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -2715,7 +2724,7 @@
       <c r="BY21" s="2"/>
       <c r="BZ21" s="2"/>
     </row>
-    <row r="22" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -2795,7 +2804,7 @@
       <c r="BY22" s="2"/>
       <c r="BZ22" s="2"/>
     </row>
-    <row r="23" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -2875,7 +2884,7 @@
       <c r="BY23" s="2"/>
       <c r="BZ23" s="2"/>
     </row>
-    <row r="24" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
@@ -2955,7 +2964,7 @@
       <c r="BY24" s="2"/>
       <c r="BZ24" s="2"/>
     </row>
-    <row r="25" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
@@ -3035,7 +3044,7 @@
       <c r="BY25" s="2"/>
       <c r="BZ25" s="2"/>
     </row>
-    <row r="26" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -3115,7 +3124,7 @@
       <c r="BY26" s="2"/>
       <c r="BZ26" s="2"/>
     </row>
-    <row r="27" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -3195,7 +3204,7 @@
       <c r="BY27" s="2"/>
       <c r="BZ27" s="2"/>
     </row>
-    <row r="28" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
@@ -3275,7 +3284,7 @@
       <c r="BY28" s="2"/>
       <c r="BZ28" s="2"/>
     </row>
-    <row r="29" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="29" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
@@ -3355,7 +3364,7 @@
       <c r="BY29" s="2"/>
       <c r="BZ29" s="2"/>
     </row>
-    <row r="30" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
@@ -3435,7 +3444,7 @@
       <c r="BY30" s="2"/>
       <c r="BZ30" s="2"/>
     </row>
-    <row r="31" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
@@ -3515,7 +3524,7 @@
       <c r="BY31" s="2"/>
       <c r="BZ31" s="2"/>
     </row>
-    <row r="32" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="32" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
@@ -3595,7 +3604,7 @@
       <c r="BY32" s="2"/>
       <c r="BZ32" s="2"/>
     </row>
-    <row r="33" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="33" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
@@ -3675,7 +3684,7 @@
       <c r="BY33" s="2"/>
       <c r="BZ33" s="2"/>
     </row>
-    <row r="34" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
@@ -3755,7 +3764,7 @@
       <c r="BY34" s="2"/>
       <c r="BZ34" s="2"/>
     </row>
-    <row r="35" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
@@ -3835,7 +3844,7 @@
       <c r="BY35" s="2"/>
       <c r="BZ35" s="2"/>
     </row>
-    <row r="36" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
@@ -3915,7 +3924,7 @@
       <c r="BY36" s="2"/>
       <c r="BZ36" s="2"/>
     </row>
-    <row r="37" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="37" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
@@ -3995,7 +4004,7 @@
       <c r="BY37" s="2"/>
       <c r="BZ37" s="2"/>
     </row>
-    <row r="38" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="38" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
@@ -4075,7 +4084,7 @@
       <c r="BY38" s="2"/>
       <c r="BZ38" s="2"/>
     </row>
-    <row r="39" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="39" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
@@ -4155,7 +4164,7 @@
       <c r="BY39" s="2"/>
       <c r="BZ39" s="2"/>
     </row>
-    <row r="40" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="40" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
@@ -4235,7 +4244,7 @@
       <c r="BY40" s="2"/>
       <c r="BZ40" s="2"/>
     </row>
-    <row r="41" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="41" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -4315,7 +4324,7 @@
       <c r="BY41" s="2"/>
       <c r="BZ41" s="2"/>
     </row>
-    <row r="42" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="42" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
@@ -4395,7 +4404,7 @@
       <c r="BY42" s="2"/>
       <c r="BZ42" s="2"/>
     </row>
-    <row r="43" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="43" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
@@ -4475,7 +4484,7 @@
       <c r="BY43" s="2"/>
       <c r="BZ43" s="2"/>
     </row>
-    <row r="44" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="44" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -4555,7 +4564,7 @@
       <c r="BY44" s="2"/>
       <c r="BZ44" s="2"/>
     </row>
-    <row r="45" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -4635,7 +4644,7 @@
       <c r="BY45" s="2"/>
       <c r="BZ45" s="2"/>
     </row>
-    <row r="46" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -4715,7 +4724,7 @@
       <c r="BY46" s="2"/>
       <c r="BZ46" s="2"/>
     </row>
-    <row r="47" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="47" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
@@ -4795,7 +4804,7 @@
       <c r="BY47" s="2"/>
       <c r="BZ47" s="2"/>
     </row>
-    <row r="48" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
@@ -4875,7 +4884,7 @@
       <c r="BY48" s="2"/>
       <c r="BZ48" s="2"/>
     </row>
-    <row r="49" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="49" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
@@ -4955,7 +4964,7 @@
       <c r="BY49" s="2"/>
       <c r="BZ49" s="2"/>
     </row>
-    <row r="50" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
@@ -5035,7 +5044,7 @@
       <c r="BY50" s="2"/>
       <c r="BZ50" s="2"/>
     </row>
-    <row r="51" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="51" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
@@ -5115,7 +5124,7 @@
       <c r="BY51" s="2"/>
       <c r="BZ51" s="2"/>
     </row>
-    <row r="52" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
@@ -5195,7 +5204,7 @@
       <c r="BY52" s="2"/>
       <c r="BZ52" s="2"/>
     </row>
-    <row r="53" ht="14.5" customHeight="1" spans="1:78" s="39" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" ht="14.5" customHeight="1" spans="1:78" s="40" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
